--- a/data/Almacen MB52/Base MB52 223.XLSX
+++ b/data/Almacen MB52/Base MB52 223.XLSX
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\04.MilicicCon\Abastecimiento\08. Compras para Obra\REPORTES\MM\Almacen MB52\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC084917-6991-41E6-88A4-E34F4696AB89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937A1846-E8FF-4BCF-A192-58D937E43A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4128" uniqueCount="508">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4110" uniqueCount="505">
   <si>
     <t>MR01</t>
   </si>
@@ -1455,15 +1455,6 @@
   </si>
   <si>
     <t>1001864</t>
-  </si>
-  <si>
-    <t>1002738</t>
-  </si>
-  <si>
-    <t>1002807</t>
-  </si>
-  <si>
-    <t>1002873</t>
   </si>
   <si>
     <t>1004250</t>
@@ -1988,7 +1979,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R685"/>
+  <dimension ref="A1:R682"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.77734375" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -2426,7 +2417,7 @@
         <v>4</v>
       </c>
       <c r="H8" s="5">
-        <v>56196.52</v>
+        <v>58406.43</v>
       </c>
       <c r="I8" s="4">
         <v>0</v>
@@ -2482,7 +2473,7 @@
         <v>4</v>
       </c>
       <c r="H9" s="5">
-        <v>11239.3</v>
+        <v>11681.29</v>
       </c>
       <c r="I9" s="4">
         <v>0</v>
@@ -5338,7 +5329,7 @@
         <v>4</v>
       </c>
       <c r="H60" s="5">
-        <v>40336.5</v>
+        <v>40336.49</v>
       </c>
       <c r="I60" s="4">
         <v>0</v>
@@ -5933,7 +5924,7 @@
     </row>
     <row r="71" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>0</v>
@@ -5989,7 +5980,7 @@
     </row>
     <row r="72" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>0</v>
@@ -7186,7 +7177,7 @@
         <v>4</v>
       </c>
       <c r="H93" s="5">
-        <v>1041176.3</v>
+        <v>1042397.25</v>
       </c>
       <c r="I93" s="4">
         <v>0</v>
@@ -7242,7 +7233,7 @@
         <v>4</v>
       </c>
       <c r="H94" s="5">
-        <v>1041176.3</v>
+        <v>1042397.25</v>
       </c>
       <c r="I94" s="4">
         <v>0</v>
@@ -7298,7 +7289,7 @@
         <v>4</v>
       </c>
       <c r="H95" s="5">
-        <v>1041176.3</v>
+        <v>1042397.25</v>
       </c>
       <c r="I95" s="4">
         <v>0</v>
@@ -8453,7 +8444,7 @@
     </row>
     <row r="116" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="B116" s="3" t="s">
         <v>0</v>
@@ -8530,7 +8521,7 @@
         <v>4</v>
       </c>
       <c r="H117" s="5">
-        <v>904821.86</v>
+        <v>902337.54</v>
       </c>
       <c r="I117" s="4">
         <v>0</v>
@@ -8565,7 +8556,7 @@
     </row>
     <row r="118" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="B118" s="3" t="s">
         <v>0</v>
@@ -8866,7 +8857,7 @@
         <v>4</v>
       </c>
       <c r="H123" s="5">
-        <v>14990.46</v>
+        <v>14990.47</v>
       </c>
       <c r="I123" s="4">
         <v>0</v>
@@ -9818,7 +9809,7 @@
         <v>4</v>
       </c>
       <c r="H140" s="5">
-        <v>31364.12</v>
+        <v>32520.09</v>
       </c>
       <c r="I140" s="4">
         <v>0</v>
@@ -9874,7 +9865,7 @@
         <v>4</v>
       </c>
       <c r="H141" s="5">
-        <v>41818.83</v>
+        <v>43360.12</v>
       </c>
       <c r="I141" s="4">
         <v>0</v>
@@ -9965,7 +9956,7 @@
     </row>
     <row r="143" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B143" s="3" t="s">
         <v>0</v>
@@ -10245,7 +10236,7 @@
     </row>
     <row r="148" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="B148" s="3" t="s">
         <v>0</v>
@@ -10938,7 +10929,7 @@
         <v>4</v>
       </c>
       <c r="H160" s="5">
-        <v>37705.629999999997</v>
+        <v>37783.69</v>
       </c>
       <c r="I160" s="4">
         <v>0</v>
@@ -10994,7 +10985,7 @@
         <v>4</v>
       </c>
       <c r="H161" s="5">
-        <v>56266.22</v>
+        <v>56263.88</v>
       </c>
       <c r="I161" s="4">
         <v>0</v>
@@ -11050,7 +11041,7 @@
         <v>4</v>
       </c>
       <c r="H162" s="5">
-        <v>36724.07</v>
+        <v>36741.879999999997</v>
       </c>
       <c r="I162" s="4">
         <v>0</v>
@@ -11106,7 +11097,7 @@
         <v>4</v>
       </c>
       <c r="H163" s="5">
-        <v>18362.03</v>
+        <v>18370.939999999999</v>
       </c>
       <c r="I163" s="4">
         <v>0</v>
@@ -11218,7 +11209,7 @@
         <v>4</v>
       </c>
       <c r="H165" s="5">
-        <v>3951.37</v>
+        <v>4240.6899999999996</v>
       </c>
       <c r="I165" s="4">
         <v>0</v>
@@ -11330,7 +11321,7 @@
         <v>4</v>
       </c>
       <c r="H167" s="5">
-        <v>50169.89</v>
+        <v>50544.01</v>
       </c>
       <c r="I167" s="4">
         <v>0</v>
@@ -11386,7 +11377,7 @@
         <v>4</v>
       </c>
       <c r="H168" s="5">
-        <v>119913.9</v>
+        <v>119872.98</v>
       </c>
       <c r="I168" s="4">
         <v>0</v>
@@ -11442,7 +11433,7 @@
         <v>4</v>
       </c>
       <c r="H169" s="5">
-        <v>33984.230000000003</v>
+        <v>34198.69</v>
       </c>
       <c r="I169" s="4">
         <v>0</v>
@@ -11498,7 +11489,7 @@
         <v>4</v>
       </c>
       <c r="H170" s="5">
-        <v>33984.230000000003</v>
+        <v>34198.69</v>
       </c>
       <c r="I170" s="4">
         <v>0</v>
@@ -11554,7 +11545,7 @@
         <v>4</v>
       </c>
       <c r="H171" s="5">
-        <v>17475.68</v>
+        <v>17289.02</v>
       </c>
       <c r="I171" s="4">
         <v>0</v>
@@ -11610,7 +11601,7 @@
         <v>4</v>
       </c>
       <c r="H172" s="5">
-        <v>17475.68</v>
+        <v>17289.02</v>
       </c>
       <c r="I172" s="4">
         <v>0</v>
@@ -11666,7 +11657,7 @@
         <v>4</v>
       </c>
       <c r="H173" s="5">
-        <v>16659.12</v>
+        <v>16838.259999999998</v>
       </c>
       <c r="I173" s="4">
         <v>0</v>
@@ -11813,7 +11804,7 @@
     </row>
     <row r="176" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>495</v>
+        <v>492</v>
       </c>
       <c r="B176" s="3" t="s">
         <v>0</v>
@@ -13346,7 +13337,7 @@
         <v>4</v>
       </c>
       <c r="H203" s="5">
-        <v>20169.23</v>
+        <v>20192.86</v>
       </c>
       <c r="I203" s="4">
         <v>0</v>
@@ -13682,7 +13673,7 @@
         <v>4</v>
       </c>
       <c r="H209" s="5">
-        <v>110716.84</v>
+        <v>109995.46</v>
       </c>
       <c r="I209" s="4">
         <v>0</v>
@@ -13738,7 +13729,7 @@
         <v>4</v>
       </c>
       <c r="H210" s="5">
-        <v>15423.07</v>
+        <v>15424.7</v>
       </c>
       <c r="I210" s="4">
         <v>0</v>
@@ -13794,7 +13785,7 @@
         <v>4</v>
       </c>
       <c r="H211" s="5">
-        <v>46269.22</v>
+        <v>46274.09</v>
       </c>
       <c r="I211" s="4">
         <v>0</v>
@@ -14277,7 +14268,7 @@
     </row>
     <row r="220" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B220" s="3" t="s">
         <v>0</v>
@@ -14333,7 +14324,7 @@
     </row>
     <row r="221" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="B221" s="3" t="s">
         <v>0</v>
@@ -14802,7 +14793,7 @@
         <v>4</v>
       </c>
       <c r="H229" s="5">
-        <v>117898.11</v>
+        <v>159669.34</v>
       </c>
       <c r="I229" s="4">
         <v>0</v>
@@ -16146,7 +16137,7 @@
         <v>4</v>
       </c>
       <c r="H253" s="5">
-        <v>28577.67</v>
+        <v>46945.13</v>
       </c>
       <c r="I253" s="4">
         <v>0</v>
@@ -16258,7 +16249,7 @@
         <v>4</v>
       </c>
       <c r="H255" s="5">
-        <v>66596.47</v>
+        <v>66596.460000000006</v>
       </c>
       <c r="I255" s="4">
         <v>0</v>
@@ -16930,7 +16921,7 @@
         <v>4</v>
       </c>
       <c r="H267" s="5">
-        <v>41926.99</v>
+        <v>42091.360000000001</v>
       </c>
       <c r="I267" s="4">
         <v>0</v>
@@ -17413,7 +17404,7 @@
     </row>
     <row r="276" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A276" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B276" s="3" t="s">
         <v>0</v>
@@ -17428,13 +17419,13 @@
         <v>3</v>
       </c>
       <c r="F276" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G276" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H276" s="5">
-        <v>10124.76</v>
+        <v>76856.3</v>
       </c>
       <c r="I276" s="4">
         <v>0</v>
@@ -17484,13 +17475,13 @@
         <v>3</v>
       </c>
       <c r="F277" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G277" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H277" s="5">
-        <v>76856.3</v>
+        <v>38428.15</v>
       </c>
       <c r="I277" s="4">
         <v>0</v>
@@ -17525,7 +17516,7 @@
     </row>
     <row r="278" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A278" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B278" s="3" t="s">
         <v>0</v>
@@ -17546,7 +17537,7 @@
         <v>4</v>
       </c>
       <c r="H278" s="5">
-        <v>38428.15</v>
+        <v>11272.02</v>
       </c>
       <c r="I278" s="4">
         <v>0</v>
@@ -17637,7 +17628,7 @@
     </row>
     <row r="280" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A280" s="3" t="s">
-        <v>160</v>
+        <v>417</v>
       </c>
       <c r="B280" s="3" t="s">
         <v>0</v>
@@ -17658,7 +17649,7 @@
         <v>4</v>
       </c>
       <c r="H280" s="5">
-        <v>11272.02</v>
+        <v>48856.23</v>
       </c>
       <c r="I280" s="4">
         <v>0</v>
@@ -17693,7 +17684,7 @@
     </row>
     <row r="281" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A281" s="3" t="s">
-        <v>417</v>
+        <v>161</v>
       </c>
       <c r="B281" s="3" t="s">
         <v>0</v>
@@ -17714,7 +17705,7 @@
         <v>4</v>
       </c>
       <c r="H281" s="5">
-        <v>48856.23</v>
+        <v>21958.47</v>
       </c>
       <c r="I281" s="4">
         <v>0</v>
@@ -17805,7 +17796,7 @@
     </row>
     <row r="283" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A283" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B283" s="3" t="s">
         <v>0</v>
@@ -17826,7 +17817,7 @@
         <v>4</v>
       </c>
       <c r="H283" s="5">
-        <v>21958.47</v>
+        <v>127198.14</v>
       </c>
       <c r="I283" s="4">
         <v>0</v>
@@ -17861,7 +17852,7 @@
     </row>
     <row r="284" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A284" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B284" s="3" t="s">
         <v>0</v>
@@ -17876,13 +17867,13 @@
         <v>3</v>
       </c>
       <c r="F284" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G284" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H284" s="5">
-        <v>127198.14</v>
+        <v>132482.51</v>
       </c>
       <c r="I284" s="4">
         <v>0</v>
@@ -17917,7 +17908,7 @@
     </row>
     <row r="285" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A285" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B285" s="3" t="s">
         <v>0</v>
@@ -17932,13 +17923,13 @@
         <v>3</v>
       </c>
       <c r="F285" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G285" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H285" s="5">
-        <v>132482.51</v>
+        <v>66541.72</v>
       </c>
       <c r="I285" s="4">
         <v>0</v>
@@ -17973,7 +17964,7 @@
     </row>
     <row r="286" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A286" s="3" t="s">
-        <v>164</v>
+        <v>372</v>
       </c>
       <c r="B286" s="3" t="s">
         <v>0</v>
@@ -17994,7 +17985,7 @@
         <v>4</v>
       </c>
       <c r="H286" s="5">
-        <v>66541.72</v>
+        <v>47750.25</v>
       </c>
       <c r="I286" s="4">
         <v>0</v>
@@ -18029,7 +18020,7 @@
     </row>
     <row r="287" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A287" s="3" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="B287" s="3" t="s">
         <v>0</v>
@@ -18050,7 +18041,7 @@
         <v>4</v>
       </c>
       <c r="H287" s="5">
-        <v>47750.25</v>
+        <v>114293.56</v>
       </c>
       <c r="I287" s="4">
         <v>0</v>
@@ -18141,7 +18132,7 @@
     </row>
     <row r="289" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A289" s="3" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B289" s="3" t="s">
         <v>0</v>
@@ -18162,7 +18153,7 @@
         <v>4</v>
       </c>
       <c r="H289" s="5">
-        <v>114293.56</v>
+        <v>92602.19</v>
       </c>
       <c r="I289" s="4">
         <v>0</v>
@@ -18218,7 +18209,7 @@
         <v>4</v>
       </c>
       <c r="H290" s="5">
-        <v>90305.98</v>
+        <v>92602.19</v>
       </c>
       <c r="I290" s="4">
         <v>0</v>
@@ -18253,7 +18244,7 @@
     </row>
     <row r="291" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A291" s="3" t="s">
-        <v>393</v>
+        <v>165</v>
       </c>
       <c r="B291" s="3" t="s">
         <v>0</v>
@@ -18268,13 +18259,13 @@
         <v>3</v>
       </c>
       <c r="F291" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G291" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H291" s="5">
-        <v>90305.98</v>
+        <v>44476.22</v>
       </c>
       <c r="I291" s="4">
         <v>0</v>
@@ -18365,7 +18356,7 @@
     </row>
     <row r="293" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A293" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B293" s="3" t="s">
         <v>0</v>
@@ -18380,13 +18371,13 @@
         <v>3</v>
       </c>
       <c r="F293" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G293" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H293" s="5">
-        <v>44476.22</v>
+        <v>1343.46</v>
       </c>
       <c r="I293" s="4">
         <v>0</v>
@@ -18421,7 +18412,7 @@
     </row>
     <row r="294" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A294" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B294" s="3" t="s">
         <v>0</v>
@@ -18442,7 +18433,7 @@
         <v>4</v>
       </c>
       <c r="H294" s="5">
-        <v>1343.46</v>
+        <v>25592.67</v>
       </c>
       <c r="I294" s="4">
         <v>0</v>
@@ -18492,13 +18483,13 @@
         <v>3</v>
       </c>
       <c r="F295" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G295" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H295" s="5">
-        <v>25592.67</v>
+        <v>51185.34</v>
       </c>
       <c r="I295" s="4">
         <v>0</v>
@@ -18533,7 +18524,7 @@
     </row>
     <row r="296" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A296" s="3" t="s">
-        <v>167</v>
+        <v>464</v>
       </c>
       <c r="B296" s="3" t="s">
         <v>0</v>
@@ -18548,13 +18539,13 @@
         <v>3</v>
       </c>
       <c r="F296" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G296" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H296" s="5">
-        <v>51185.34</v>
+        <v>121789.45</v>
       </c>
       <c r="I296" s="4">
         <v>0</v>
@@ -18645,7 +18636,7 @@
     </row>
     <row r="298" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A298" s="3" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B298" s="3" t="s">
         <v>0</v>
@@ -18666,7 +18657,7 @@
         <v>4</v>
       </c>
       <c r="H298" s="5">
-        <v>121789.45</v>
+        <v>98685.99</v>
       </c>
       <c r="I298" s="4">
         <v>0</v>
@@ -18701,7 +18692,7 @@
     </row>
     <row r="299" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A299" s="3" t="s">
-        <v>465</v>
+        <v>168</v>
       </c>
       <c r="B299" s="3" t="s">
         <v>0</v>
@@ -18722,7 +18713,7 @@
         <v>4</v>
       </c>
       <c r="H299" s="5">
-        <v>98685.99</v>
+        <v>28474.3</v>
       </c>
       <c r="I299" s="4">
         <v>0</v>
@@ -18757,7 +18748,7 @@
     </row>
     <row r="300" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A300" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B300" s="3" t="s">
         <v>0</v>
@@ -18778,7 +18769,7 @@
         <v>4</v>
       </c>
       <c r="H300" s="5">
-        <v>28474.3</v>
+        <v>11957.02</v>
       </c>
       <c r="I300" s="4">
         <v>0</v>
@@ -18813,7 +18804,7 @@
     </row>
     <row r="301" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A301" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B301" s="3" t="s">
         <v>0</v>
@@ -18828,13 +18819,13 @@
         <v>3</v>
       </c>
       <c r="F301" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G301" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H301" s="5">
-        <v>11957.02</v>
+        <v>17086.169999999998</v>
       </c>
       <c r="I301" s="4">
         <v>0</v>
@@ -18869,7 +18860,7 @@
     </row>
     <row r="302" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A302" s="3" t="s">
-        <v>170</v>
+        <v>418</v>
       </c>
       <c r="B302" s="3" t="s">
         <v>0</v>
@@ -18884,13 +18875,13 @@
         <v>3</v>
       </c>
       <c r="F302" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G302" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H302" s="5">
-        <v>17086.169999999998</v>
+        <v>62200.91</v>
       </c>
       <c r="I302" s="4">
         <v>0</v>
@@ -18925,7 +18916,7 @@
     </row>
     <row r="303" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A303" s="3" t="s">
-        <v>418</v>
+        <v>381</v>
       </c>
       <c r="B303" s="3" t="s">
         <v>0</v>
@@ -18946,7 +18937,7 @@
         <v>4</v>
       </c>
       <c r="H303" s="5">
-        <v>62200.91</v>
+        <v>40497.69</v>
       </c>
       <c r="I303" s="4">
         <v>0</v>
@@ -18981,7 +18972,7 @@
     </row>
     <row r="304" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A304" s="3" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B304" s="3" t="s">
         <v>0</v>
@@ -18996,13 +18987,13 @@
         <v>3</v>
       </c>
       <c r="F304" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G304" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H304" s="5">
-        <v>8706.84</v>
+        <v>40905.160000000003</v>
       </c>
       <c r="I304" s="4">
         <v>0</v>
@@ -19037,7 +19028,7 @@
     </row>
     <row r="305" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A305" s="3" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B305" s="3" t="s">
         <v>0</v>
@@ -19058,7 +19049,7 @@
         <v>4</v>
       </c>
       <c r="H305" s="5">
-        <v>40497.69</v>
+        <v>35480.6</v>
       </c>
       <c r="I305" s="4">
         <v>0</v>
@@ -19093,7 +19084,7 @@
     </row>
     <row r="306" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A306" s="3" t="s">
-        <v>466</v>
+        <v>388</v>
       </c>
       <c r="B306" s="3" t="s">
         <v>0</v>
@@ -19108,13 +19099,13 @@
         <v>3</v>
       </c>
       <c r="F306" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G306" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H306" s="5">
-        <v>40905.160000000003</v>
+        <v>39428.28</v>
       </c>
       <c r="I306" s="4">
         <v>0</v>
@@ -19149,7 +19140,7 @@
     </row>
     <row r="307" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A307" s="3" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B307" s="3" t="s">
         <v>0</v>
@@ -19170,7 +19161,7 @@
         <v>4</v>
       </c>
       <c r="H307" s="5">
-        <v>35480.6</v>
+        <v>39428.28</v>
       </c>
       <c r="I307" s="4">
         <v>0</v>
@@ -19205,7 +19196,7 @@
     </row>
     <row r="308" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A308" s="3" t="s">
-        <v>388</v>
+        <v>419</v>
       </c>
       <c r="B308" s="3" t="s">
         <v>0</v>
@@ -19226,7 +19217,7 @@
         <v>4</v>
       </c>
       <c r="H308" s="5">
-        <v>39700.54</v>
+        <v>28857.599999999999</v>
       </c>
       <c r="I308" s="4">
         <v>0</v>
@@ -19261,7 +19252,7 @@
     </row>
     <row r="309" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A309" s="3" t="s">
-        <v>388</v>
+        <v>171</v>
       </c>
       <c r="B309" s="3" t="s">
         <v>0</v>
@@ -19276,19 +19267,19 @@
         <v>3</v>
       </c>
       <c r="F309" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G309" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H309" s="5">
-        <v>39700.54</v>
+        <v>0</v>
       </c>
       <c r="I309" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J309" s="5">
-        <v>0</v>
+        <v>90.83</v>
       </c>
       <c r="K309" s="4">
         <v>0</v>
@@ -19317,7 +19308,7 @@
     </row>
     <row r="310" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A310" s="3" t="s">
-        <v>419</v>
+        <v>383</v>
       </c>
       <c r="B310" s="3" t="s">
         <v>0</v>
@@ -19338,7 +19329,7 @@
         <v>4</v>
       </c>
       <c r="H310" s="5">
-        <v>28857.599999999999</v>
+        <v>13750.4</v>
       </c>
       <c r="I310" s="4">
         <v>0</v>
@@ -19373,7 +19364,7 @@
     </row>
     <row r="311" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A311" s="3" t="s">
-        <v>171</v>
+        <v>383</v>
       </c>
       <c r="B311" s="3" t="s">
         <v>0</v>
@@ -19388,19 +19379,19 @@
         <v>3</v>
       </c>
       <c r="F311" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G311" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H311" s="5">
-        <v>0</v>
+        <v>13750.4</v>
       </c>
       <c r="I311" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J311" s="5">
-        <v>90.83</v>
+        <v>0</v>
       </c>
       <c r="K311" s="4">
         <v>0</v>
@@ -19429,7 +19420,7 @@
     </row>
     <row r="312" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A312" s="3" t="s">
-        <v>383</v>
+        <v>365</v>
       </c>
       <c r="B312" s="3" t="s">
         <v>0</v>
@@ -19450,7 +19441,7 @@
         <v>4</v>
       </c>
       <c r="H312" s="5">
-        <v>13750.4</v>
+        <v>115593.64</v>
       </c>
       <c r="I312" s="4">
         <v>0</v>
@@ -19485,7 +19476,7 @@
     </row>
     <row r="313" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A313" s="3" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B313" s="3" t="s">
         <v>0</v>
@@ -19506,7 +19497,7 @@
         <v>4</v>
       </c>
       <c r="H313" s="5">
-        <v>13750.4</v>
+        <v>12828.48</v>
       </c>
       <c r="I313" s="4">
         <v>0</v>
@@ -19541,7 +19532,7 @@
     </row>
     <row r="314" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A314" s="3" t="s">
-        <v>365</v>
+        <v>384</v>
       </c>
       <c r="B314" s="3" t="s">
         <v>0</v>
@@ -19562,7 +19553,7 @@
         <v>4</v>
       </c>
       <c r="H314" s="5">
-        <v>115593.64</v>
+        <v>12828.48</v>
       </c>
       <c r="I314" s="4">
         <v>0</v>
@@ -19597,7 +19588,7 @@
     </row>
     <row r="315" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A315" s="3" t="s">
-        <v>475</v>
+        <v>172</v>
       </c>
       <c r="B315" s="3" t="s">
         <v>0</v>
@@ -19618,7 +19609,7 @@
         <v>4</v>
       </c>
       <c r="H315" s="5">
-        <v>14667.91</v>
+        <v>75857.38</v>
       </c>
       <c r="I315" s="4">
         <v>0</v>
@@ -19653,7 +19644,7 @@
     </row>
     <row r="316" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A316" s="3" t="s">
-        <v>384</v>
+        <v>173</v>
       </c>
       <c r="B316" s="3" t="s">
         <v>0</v>
@@ -19674,7 +19665,7 @@
         <v>4</v>
       </c>
       <c r="H316" s="5">
-        <v>12828.48</v>
+        <v>12488.05</v>
       </c>
       <c r="I316" s="4">
         <v>0</v>
@@ -19709,7 +19700,7 @@
     </row>
     <row r="317" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A317" s="3" t="s">
-        <v>384</v>
+        <v>174</v>
       </c>
       <c r="B317" s="3" t="s">
         <v>0</v>
@@ -19730,7 +19721,7 @@
         <v>4</v>
       </c>
       <c r="H317" s="5">
-        <v>12828.48</v>
+        <v>55895.44</v>
       </c>
       <c r="I317" s="4">
         <v>0</v>
@@ -19765,7 +19756,7 @@
     </row>
     <row r="318" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A318" s="3" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="B318" s="3" t="s">
         <v>0</v>
@@ -19786,7 +19777,7 @@
         <v>4</v>
       </c>
       <c r="H318" s="5">
-        <v>75857.38</v>
+        <v>53894.01</v>
       </c>
       <c r="I318" s="4">
         <v>0</v>
@@ -19821,7 +19812,7 @@
     </row>
     <row r="319" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A319" s="3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="B319" s="3" t="s">
         <v>0</v>
@@ -19836,13 +19827,13 @@
         <v>3</v>
       </c>
       <c r="F319" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G319" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H319" s="5">
-        <v>12488.05</v>
+        <v>28273.87</v>
       </c>
       <c r="I319" s="4">
         <v>0</v>
@@ -19877,7 +19868,7 @@
     </row>
     <row r="320" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A320" s="3" t="s">
-        <v>173</v>
+        <v>458</v>
       </c>
       <c r="B320" s="3" t="s">
         <v>0</v>
@@ -19898,7 +19889,7 @@
         <v>4</v>
       </c>
       <c r="H320" s="5">
-        <v>12488.05</v>
+        <v>128429.04</v>
       </c>
       <c r="I320" s="4">
         <v>0</v>
@@ -19933,7 +19924,7 @@
     </row>
     <row r="321" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A321" s="3" t="s">
-        <v>174</v>
+        <v>479</v>
       </c>
       <c r="B321" s="3" t="s">
         <v>0</v>
@@ -19954,7 +19945,7 @@
         <v>4</v>
       </c>
       <c r="H321" s="5">
-        <v>55895.44</v>
+        <v>40803.14</v>
       </c>
       <c r="I321" s="4">
         <v>0</v>
@@ -19989,7 +19980,7 @@
     </row>
     <row r="322" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A322" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B322" s="3" t="s">
         <v>0</v>
@@ -20010,7 +20001,7 @@
         <v>4</v>
       </c>
       <c r="H322" s="5">
-        <v>53894.01</v>
+        <v>30409.42</v>
       </c>
       <c r="I322" s="4">
         <v>0</v>
@@ -20045,7 +20036,7 @@
     </row>
     <row r="323" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A323" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B323" s="3" t="s">
         <v>0</v>
@@ -20066,7 +20057,7 @@
         <v>4</v>
       </c>
       <c r="H323" s="5">
-        <v>28273.87</v>
+        <v>139259.92000000001</v>
       </c>
       <c r="I323" s="4">
         <v>0</v>
@@ -20101,7 +20092,7 @@
     </row>
     <row r="324" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A324" s="3" t="s">
-        <v>476</v>
+        <v>493</v>
       </c>
       <c r="B324" s="3" t="s">
         <v>0</v>
@@ -20122,7 +20113,7 @@
         <v>4</v>
       </c>
       <c r="H324" s="5">
-        <v>70.739999999999995</v>
+        <v>81571.539999999994</v>
       </c>
       <c r="I324" s="4">
         <v>0</v>
@@ -20157,7 +20148,7 @@
     </row>
     <row r="325" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A325" s="3" t="s">
-        <v>458</v>
+        <v>494</v>
       </c>
       <c r="B325" s="3" t="s">
         <v>0</v>
@@ -20172,13 +20163,13 @@
         <v>3</v>
       </c>
       <c r="F325" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G325" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H325" s="5">
-        <v>128429.04</v>
+        <v>359523.22</v>
       </c>
       <c r="I325" s="4">
         <v>0</v>
@@ -20213,7 +20204,7 @@
     </row>
     <row r="326" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A326" s="3" t="s">
-        <v>482</v>
+        <v>179</v>
       </c>
       <c r="B326" s="3" t="s">
         <v>0</v>
@@ -20234,7 +20225,7 @@
         <v>4</v>
       </c>
       <c r="H326" s="5">
-        <v>40803.14</v>
+        <v>18383.13</v>
       </c>
       <c r="I326" s="4">
         <v>0</v>
@@ -20269,7 +20260,7 @@
     </row>
     <row r="327" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A327" s="3" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="B327" s="3" t="s">
         <v>0</v>
@@ -20290,7 +20281,7 @@
         <v>4</v>
       </c>
       <c r="H327" s="5">
-        <v>30409.42</v>
+        <v>30852.25</v>
       </c>
       <c r="I327" s="4">
         <v>0</v>
@@ -20325,7 +20316,7 @@
     </row>
     <row r="328" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A328" s="3" t="s">
-        <v>178</v>
+        <v>389</v>
       </c>
       <c r="B328" s="3" t="s">
         <v>0</v>
@@ -20340,13 +20331,13 @@
         <v>3</v>
       </c>
       <c r="F328" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G328" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H328" s="5">
-        <v>139259.92000000001</v>
+        <v>37082.019999999997</v>
       </c>
       <c r="I328" s="4">
         <v>0</v>
@@ -20381,7 +20372,7 @@
     </row>
     <row r="329" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A329" s="3" t="s">
-        <v>496</v>
+        <v>389</v>
       </c>
       <c r="B329" s="3" t="s">
         <v>0</v>
@@ -20402,7 +20393,7 @@
         <v>4</v>
       </c>
       <c r="H329" s="5">
-        <v>75533.509999999995</v>
+        <v>37082.019999999997</v>
       </c>
       <c r="I329" s="4">
         <v>0</v>
@@ -20437,7 +20428,7 @@
     </row>
     <row r="330" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A330" s="3" t="s">
-        <v>497</v>
+        <v>181</v>
       </c>
       <c r="B330" s="3" t="s">
         <v>0</v>
@@ -20452,13 +20443,13 @@
         <v>3</v>
       </c>
       <c r="F330" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G330" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H330" s="5">
-        <v>359523.22</v>
+        <v>28542.74</v>
       </c>
       <c r="I330" s="4">
         <v>0</v>
@@ -20493,7 +20484,7 @@
     </row>
     <row r="331" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A331" s="3" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B331" s="3" t="s">
         <v>0</v>
@@ -20508,13 +20499,13 @@
         <v>3</v>
       </c>
       <c r="F331" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G331" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H331" s="5">
-        <v>18383.13</v>
+        <v>133091.01</v>
       </c>
       <c r="I331" s="4">
         <v>0</v>
@@ -20549,7 +20540,7 @@
     </row>
     <row r="332" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A332" s="3" t="s">
-        <v>180</v>
+        <v>385</v>
       </c>
       <c r="B332" s="3" t="s">
         <v>0</v>
@@ -20570,7 +20561,7 @@
         <v>4</v>
       </c>
       <c r="H332" s="5">
-        <v>30852.25</v>
+        <v>16464.580000000002</v>
       </c>
       <c r="I332" s="4">
         <v>0</v>
@@ -20605,7 +20596,7 @@
     </row>
     <row r="333" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A333" s="3" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B333" s="3" t="s">
         <v>0</v>
@@ -20626,7 +20617,7 @@
         <v>4</v>
       </c>
       <c r="H333" s="5">
-        <v>37082.019999999997</v>
+        <v>23670.92</v>
       </c>
       <c r="I333" s="4">
         <v>0</v>
@@ -20661,7 +20652,7 @@
     </row>
     <row r="334" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A334" s="3" t="s">
-        <v>389</v>
+        <v>467</v>
       </c>
       <c r="B334" s="3" t="s">
         <v>0</v>
@@ -20682,7 +20673,7 @@
         <v>4</v>
       </c>
       <c r="H334" s="5">
-        <v>37082.019999999997</v>
+        <v>40919.47</v>
       </c>
       <c r="I334" s="4">
         <v>0</v>
@@ -20717,7 +20708,7 @@
     </row>
     <row r="335" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A335" s="3" t="s">
-        <v>181</v>
+        <v>467</v>
       </c>
       <c r="B335" s="3" t="s">
         <v>0</v>
@@ -20738,7 +20729,7 @@
         <v>4</v>
       </c>
       <c r="H335" s="5">
-        <v>28542.74</v>
+        <v>40919.47</v>
       </c>
       <c r="I335" s="4">
         <v>0</v>
@@ -20773,7 +20764,7 @@
     </row>
     <row r="336" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A336" s="3" t="s">
-        <v>182</v>
+        <v>468</v>
       </c>
       <c r="B336" s="3" t="s">
         <v>0</v>
@@ -20788,13 +20779,13 @@
         <v>3</v>
       </c>
       <c r="F336" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G336" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H336" s="5">
-        <v>133091.01</v>
+        <v>121295.22</v>
       </c>
       <c r="I336" s="4">
         <v>0</v>
@@ -20829,7 +20820,7 @@
     </row>
     <row r="337" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A337" s="3" t="s">
-        <v>385</v>
+        <v>468</v>
       </c>
       <c r="B337" s="3" t="s">
         <v>0</v>
@@ -20850,7 +20841,7 @@
         <v>4</v>
       </c>
       <c r="H337" s="5">
-        <v>16464.580000000002</v>
+        <v>121295.22</v>
       </c>
       <c r="I337" s="4">
         <v>0</v>
@@ -20885,7 +20876,7 @@
     </row>
     <row r="338" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A338" s="3" t="s">
-        <v>386</v>
+        <v>469</v>
       </c>
       <c r="B338" s="3" t="s">
         <v>0</v>
@@ -20900,13 +20891,13 @@
         <v>3</v>
       </c>
       <c r="F338" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G338" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H338" s="5">
-        <v>23670.92</v>
+        <v>79472.39</v>
       </c>
       <c r="I338" s="4">
         <v>0</v>
@@ -20941,7 +20932,7 @@
     </row>
     <row r="339" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A339" s="3" t="s">
-        <v>467</v>
+        <v>420</v>
       </c>
       <c r="B339" s="3" t="s">
         <v>0</v>
@@ -20962,7 +20953,7 @@
         <v>4</v>
       </c>
       <c r="H339" s="5">
-        <v>40919.47</v>
+        <v>151943.65</v>
       </c>
       <c r="I339" s="4">
         <v>0</v>
@@ -20997,7 +20988,7 @@
     </row>
     <row r="340" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A340" s="3" t="s">
-        <v>467</v>
+        <v>421</v>
       </c>
       <c r="B340" s="3" t="s">
         <v>0</v>
@@ -21018,7 +21009,7 @@
         <v>4</v>
       </c>
       <c r="H340" s="5">
-        <v>40919.47</v>
+        <v>119959.65</v>
       </c>
       <c r="I340" s="4">
         <v>0</v>
@@ -21053,7 +21044,7 @@
     </row>
     <row r="341" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A341" s="3" t="s">
-        <v>468</v>
+        <v>183</v>
       </c>
       <c r="B341" s="3" t="s">
         <v>0</v>
@@ -21074,7 +21065,7 @@
         <v>4</v>
       </c>
       <c r="H341" s="5">
-        <v>121295.22</v>
+        <v>4038.17</v>
       </c>
       <c r="I341" s="4">
         <v>0</v>
@@ -21109,7 +21100,7 @@
     </row>
     <row r="342" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A342" s="3" t="s">
-        <v>468</v>
+        <v>183</v>
       </c>
       <c r="B342" s="3" t="s">
         <v>0</v>
@@ -21130,7 +21121,7 @@
         <v>4</v>
       </c>
       <c r="H342" s="5">
-        <v>121295.22</v>
+        <v>4038.17</v>
       </c>
       <c r="I342" s="4">
         <v>0</v>
@@ -21165,7 +21156,7 @@
     </row>
     <row r="343" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A343" s="3" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B343" s="3" t="s">
         <v>0</v>
@@ -21180,13 +21171,13 @@
         <v>3</v>
       </c>
       <c r="F343" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G343" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H343" s="5">
-        <v>79472.39</v>
+        <v>87507.95</v>
       </c>
       <c r="I343" s="4">
         <v>0</v>
@@ -21221,7 +21212,7 @@
     </row>
     <row r="344" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A344" s="3" t="s">
-        <v>420</v>
+        <v>184</v>
       </c>
       <c r="B344" s="3" t="s">
         <v>0</v>
@@ -21242,7 +21233,7 @@
         <v>4</v>
       </c>
       <c r="H344" s="5">
-        <v>151943.65</v>
+        <v>57406.66</v>
       </c>
       <c r="I344" s="4">
         <v>0</v>
@@ -21277,7 +21268,7 @@
     </row>
     <row r="345" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A345" s="3" t="s">
-        <v>421</v>
+        <v>185</v>
       </c>
       <c r="B345" s="3" t="s">
         <v>0</v>
@@ -21298,7 +21289,7 @@
         <v>4</v>
       </c>
       <c r="H345" s="5">
-        <v>119959.65</v>
+        <v>24416.73</v>
       </c>
       <c r="I345" s="4">
         <v>0</v>
@@ -21333,7 +21324,7 @@
     </row>
     <row r="346" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A346" s="3" t="s">
-        <v>183</v>
+        <v>390</v>
       </c>
       <c r="B346" s="3" t="s">
         <v>0</v>
@@ -21348,13 +21339,13 @@
         <v>3</v>
       </c>
       <c r="F346" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G346" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H346" s="5">
-        <v>4038.17</v>
+        <v>71157.98</v>
       </c>
       <c r="I346" s="4">
         <v>0</v>
@@ -21389,7 +21380,7 @@
     </row>
     <row r="347" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A347" s="3" t="s">
-        <v>183</v>
+        <v>495</v>
       </c>
       <c r="B347" s="3" t="s">
         <v>0</v>
@@ -21410,7 +21401,7 @@
         <v>4</v>
       </c>
       <c r="H347" s="5">
-        <v>4038.17</v>
+        <v>22067.89</v>
       </c>
       <c r="I347" s="4">
         <v>0</v>
@@ -21445,7 +21436,7 @@
     </row>
     <row r="348" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A348" s="3" t="s">
-        <v>470</v>
+        <v>391</v>
       </c>
       <c r="B348" s="3" t="s">
         <v>0</v>
@@ -21460,13 +21451,13 @@
         <v>3</v>
       </c>
       <c r="F348" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G348" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H348" s="5">
-        <v>87507.95</v>
+        <v>85868.68</v>
       </c>
       <c r="I348" s="4">
         <v>0</v>
@@ -21501,7 +21492,7 @@
     </row>
     <row r="349" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A349" s="3" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B349" s="3" t="s">
         <v>0</v>
@@ -21516,13 +21507,13 @@
         <v>3</v>
       </c>
       <c r="F349" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G349" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H349" s="5">
-        <v>57406.66</v>
+        <v>55356.72</v>
       </c>
       <c r="I349" s="4">
         <v>0</v>
@@ -21557,7 +21548,7 @@
     </row>
     <row r="350" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A350" s="3" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B350" s="3" t="s">
         <v>0</v>
@@ -21572,13 +21563,13 @@
         <v>3</v>
       </c>
       <c r="F350" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G350" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H350" s="5">
-        <v>24416.73</v>
+        <v>355314.77</v>
       </c>
       <c r="I350" s="4">
         <v>0</v>
@@ -21613,7 +21604,7 @@
     </row>
     <row r="351" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A351" s="3" t="s">
-        <v>390</v>
+        <v>188</v>
       </c>
       <c r="B351" s="3" t="s">
         <v>0</v>
@@ -21634,7 +21625,7 @@
         <v>4</v>
       </c>
       <c r="H351" s="5">
-        <v>71157.98</v>
+        <v>209757.71</v>
       </c>
       <c r="I351" s="4">
         <v>0</v>
@@ -21669,7 +21660,7 @@
     </row>
     <row r="352" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A352" s="3" t="s">
-        <v>498</v>
+        <v>189</v>
       </c>
       <c r="B352" s="3" t="s">
         <v>0</v>
@@ -21684,13 +21675,13 @@
         <v>3</v>
       </c>
       <c r="F352" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G352" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H352" s="5">
-        <v>22067.89</v>
+        <v>84284.37</v>
       </c>
       <c r="I352" s="4">
         <v>0</v>
@@ -21725,7 +21716,7 @@
     </row>
     <row r="353" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A353" s="3" t="s">
-        <v>391</v>
+        <v>190</v>
       </c>
       <c r="B353" s="3" t="s">
         <v>0</v>
@@ -21740,13 +21731,13 @@
         <v>3</v>
       </c>
       <c r="F353" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G353" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H353" s="5">
-        <v>85868.68</v>
+        <v>52363.94</v>
       </c>
       <c r="I353" s="4">
         <v>0</v>
@@ -21781,7 +21772,7 @@
     </row>
     <row r="354" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A354" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B354" s="3" t="s">
         <v>0</v>
@@ -21796,13 +21787,13 @@
         <v>3</v>
       </c>
       <c r="F354" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G354" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H354" s="5">
-        <v>55356.72</v>
+        <v>52363.94</v>
       </c>
       <c r="I354" s="4">
         <v>0</v>
@@ -21837,7 +21828,7 @@
     </row>
     <row r="355" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A355" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B355" s="3" t="s">
         <v>0</v>
@@ -21852,13 +21843,13 @@
         <v>3</v>
       </c>
       <c r="F355" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G355" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H355" s="5">
-        <v>355314.77</v>
+        <v>7070.24</v>
       </c>
       <c r="I355" s="4">
         <v>0</v>
@@ -21893,7 +21884,7 @@
     </row>
     <row r="356" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A356" s="3" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B356" s="3" t="s">
         <v>0</v>
@@ -21908,13 +21899,13 @@
         <v>3</v>
       </c>
       <c r="F356" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G356" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H356" s="5">
-        <v>209757.71</v>
+        <v>75084.06</v>
       </c>
       <c r="I356" s="4">
         <v>0</v>
@@ -21949,7 +21940,7 @@
     </row>
     <row r="357" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A357" s="3" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B357" s="3" t="s">
         <v>0</v>
@@ -21964,13 +21955,13 @@
         <v>3</v>
       </c>
       <c r="F357" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G357" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H357" s="5">
-        <v>84284.37</v>
+        <v>154034.98000000001</v>
       </c>
       <c r="I357" s="4">
         <v>0</v>
@@ -22005,7 +21996,7 @@
     </row>
     <row r="358" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A358" s="3" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B358" s="3" t="s">
         <v>0</v>
@@ -22026,7 +22017,7 @@
         <v>4</v>
       </c>
       <c r="H358" s="5">
-        <v>52363.94</v>
+        <v>154034.98000000001</v>
       </c>
       <c r="I358" s="4">
         <v>0</v>
@@ -22061,7 +22052,7 @@
     </row>
     <row r="359" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A359" s="3" t="s">
-        <v>190</v>
+        <v>480</v>
       </c>
       <c r="B359" s="3" t="s">
         <v>0</v>
@@ -22082,7 +22073,7 @@
         <v>4</v>
       </c>
       <c r="H359" s="5">
-        <v>52363.94</v>
+        <v>141652.51</v>
       </c>
       <c r="I359" s="4">
         <v>0</v>
@@ -22117,7 +22108,7 @@
     </row>
     <row r="360" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A360" s="3" t="s">
-        <v>191</v>
+        <v>358</v>
       </c>
       <c r="B360" s="3" t="s">
         <v>0</v>
@@ -22138,7 +22129,7 @@
         <v>4</v>
       </c>
       <c r="H360" s="5">
-        <v>7070.24</v>
+        <v>272488.15000000002</v>
       </c>
       <c r="I360" s="4">
         <v>0</v>
@@ -22173,7 +22164,7 @@
     </row>
     <row r="361" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A361" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B361" s="3" t="s">
         <v>0</v>
@@ -22194,7 +22185,7 @@
         <v>4</v>
       </c>
       <c r="H361" s="5">
-        <v>75084.06</v>
+        <v>4969.1400000000003</v>
       </c>
       <c r="I361" s="4">
         <v>0</v>
@@ -22229,7 +22220,7 @@
     </row>
     <row r="362" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A362" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B362" s="3" t="s">
         <v>0</v>
@@ -22244,13 +22235,13 @@
         <v>3</v>
       </c>
       <c r="F362" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G362" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H362" s="5">
-        <v>154034.98000000001</v>
+        <v>9262.36</v>
       </c>
       <c r="I362" s="4">
         <v>0</v>
@@ -22285,7 +22276,7 @@
     </row>
     <row r="363" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A363" s="3" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="B363" s="3" t="s">
         <v>0</v>
@@ -22300,13 +22291,13 @@
         <v>3</v>
       </c>
       <c r="F363" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G363" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H363" s="5">
-        <v>154034.98000000001</v>
+        <v>93791.32</v>
       </c>
       <c r="I363" s="4">
         <v>0</v>
@@ -22341,7 +22332,7 @@
     </row>
     <row r="364" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A364" s="3" t="s">
-        <v>483</v>
+        <v>197</v>
       </c>
       <c r="B364" s="3" t="s">
         <v>0</v>
@@ -22356,13 +22347,13 @@
         <v>3</v>
       </c>
       <c r="F364" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G364" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H364" s="5">
-        <v>141165.51999999999</v>
+        <v>37031.300000000003</v>
       </c>
       <c r="I364" s="4">
         <v>0</v>
@@ -22397,7 +22388,7 @@
     </row>
     <row r="365" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A365" s="3" t="s">
-        <v>358</v>
+        <v>198</v>
       </c>
       <c r="B365" s="3" t="s">
         <v>0</v>
@@ -22412,13 +22403,13 @@
         <v>3</v>
       </c>
       <c r="F365" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G365" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H365" s="5">
-        <v>267044.28000000003</v>
+        <v>20078.580000000002</v>
       </c>
       <c r="I365" s="4">
         <v>0</v>
@@ -22453,7 +22444,7 @@
     </row>
     <row r="366" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A366" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="B366" s="3" t="s">
         <v>0</v>
@@ -22468,13 +22459,13 @@
         <v>3</v>
       </c>
       <c r="F366" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G366" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H366" s="5">
-        <v>4969.1400000000003</v>
+        <v>28550.16</v>
       </c>
       <c r="I366" s="4">
         <v>0</v>
@@ -22509,7 +22500,7 @@
     </row>
     <row r="367" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A367" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="B367" s="3" t="s">
         <v>0</v>
@@ -22530,7 +22521,7 @@
         <v>4</v>
       </c>
       <c r="H367" s="5">
-        <v>9262.36</v>
+        <v>22284.49</v>
       </c>
       <c r="I367" s="4">
         <v>0</v>
@@ -22565,7 +22556,7 @@
     </row>
     <row r="368" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A368" s="3" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="B368" s="3" t="s">
         <v>0</v>
@@ -22580,13 +22571,13 @@
         <v>3</v>
       </c>
       <c r="F368" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G368" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H368" s="5">
-        <v>93791.32</v>
+        <v>241167.82</v>
       </c>
       <c r="I368" s="4">
         <v>0</v>
@@ -22621,7 +22612,7 @@
     </row>
     <row r="369" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A369" s="3" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="B369" s="3" t="s">
         <v>0</v>
@@ -22636,13 +22627,13 @@
         <v>3</v>
       </c>
       <c r="F369" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G369" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H369" s="5">
-        <v>37031.300000000003</v>
+        <v>73601.7</v>
       </c>
       <c r="I369" s="4">
         <v>0</v>
@@ -22677,7 +22668,7 @@
     </row>
     <row r="370" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A370" s="3" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="B370" s="3" t="s">
         <v>0</v>
@@ -22692,13 +22683,13 @@
         <v>3</v>
       </c>
       <c r="F370" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G370" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H370" s="5">
-        <v>20078.580000000002</v>
+        <v>83485.59</v>
       </c>
       <c r="I370" s="4">
         <v>0</v>
@@ -22733,7 +22724,7 @@
     </row>
     <row r="371" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A371" s="3" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="B371" s="3" t="s">
         <v>0</v>
@@ -22748,13 +22739,13 @@
         <v>3</v>
       </c>
       <c r="F371" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G371" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H371" s="5">
-        <v>28550.16</v>
+        <v>66806.53</v>
       </c>
       <c r="I371" s="4">
         <v>0</v>
@@ -22789,7 +22780,7 @@
     </row>
     <row r="372" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A372" s="3" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B372" s="3" t="s">
         <v>0</v>
@@ -22804,13 +22795,13 @@
         <v>3</v>
       </c>
       <c r="F372" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G372" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H372" s="5">
-        <v>22284.49</v>
+        <v>73888.179999999993</v>
       </c>
       <c r="I372" s="4">
         <v>0</v>
@@ -22845,7 +22836,7 @@
     </row>
     <row r="373" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A373" s="3" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B373" s="3" t="s">
         <v>0</v>
@@ -22866,7 +22857,7 @@
         <v>4</v>
       </c>
       <c r="H373" s="5">
-        <v>241167.82</v>
+        <v>88163.4</v>
       </c>
       <c r="I373" s="4">
         <v>0</v>
@@ -22901,7 +22892,7 @@
     </row>
     <row r="374" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A374" s="3" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="B374" s="3" t="s">
         <v>0</v>
@@ -22922,7 +22913,7 @@
         <v>4</v>
       </c>
       <c r="H374" s="5">
-        <v>73601.7</v>
+        <v>8544.73</v>
       </c>
       <c r="I374" s="4">
         <v>0</v>
@@ -22957,7 +22948,7 @@
     </row>
     <row r="375" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A375" s="3" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="B375" s="3" t="s">
         <v>0</v>
@@ -22972,13 +22963,13 @@
         <v>3</v>
       </c>
       <c r="F375" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G375" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H375" s="5">
-        <v>83485.59</v>
+        <v>107050.01</v>
       </c>
       <c r="I375" s="4">
         <v>0</v>
@@ -23013,7 +23004,7 @@
     </row>
     <row r="376" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A376" s="3" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="B376" s="3" t="s">
         <v>0</v>
@@ -23028,13 +23019,13 @@
         <v>3</v>
       </c>
       <c r="F376" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G376" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H376" s="5">
-        <v>66806.53</v>
+        <v>64142.83</v>
       </c>
       <c r="I376" s="4">
         <v>0</v>
@@ -23069,7 +23060,7 @@
     </row>
     <row r="377" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A377" s="3" t="s">
-        <v>205</v>
+        <v>359</v>
       </c>
       <c r="B377" s="3" t="s">
         <v>0</v>
@@ -23084,13 +23075,13 @@
         <v>3</v>
       </c>
       <c r="F377" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G377" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H377" s="5">
-        <v>73888.179999999993</v>
+        <v>175961.76</v>
       </c>
       <c r="I377" s="4">
         <v>0</v>
@@ -23125,7 +23116,7 @@
     </row>
     <row r="378" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A378" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B378" s="3" t="s">
         <v>0</v>
@@ -23140,13 +23131,13 @@
         <v>3</v>
       </c>
       <c r="F378" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G378" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H378" s="5">
-        <v>88163.4</v>
+        <v>86980.72</v>
       </c>
       <c r="I378" s="4">
         <v>0</v>
@@ -23181,7 +23172,7 @@
     </row>
     <row r="379" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A379" s="3" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="B379" s="3" t="s">
         <v>0</v>
@@ -23202,7 +23193,7 @@
         <v>4</v>
       </c>
       <c r="H379" s="5">
-        <v>8544.73</v>
+        <v>17485.77</v>
       </c>
       <c r="I379" s="4">
         <v>0</v>
@@ -23237,7 +23228,7 @@
     </row>
     <row r="380" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A380" s="3" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B380" s="3" t="s">
         <v>0</v>
@@ -23252,13 +23243,13 @@
         <v>3</v>
       </c>
       <c r="F380" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G380" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H380" s="5">
-        <v>107050.01</v>
+        <v>333177.46000000002</v>
       </c>
       <c r="I380" s="4">
         <v>0</v>
@@ -23293,7 +23284,7 @@
     </row>
     <row r="381" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A381" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B381" s="3" t="s">
         <v>0</v>
@@ -23314,7 +23305,7 @@
         <v>4</v>
       </c>
       <c r="H381" s="5">
-        <v>64142.83</v>
+        <v>54182.879999999997</v>
       </c>
       <c r="I381" s="4">
         <v>0</v>
@@ -23349,7 +23340,7 @@
     </row>
     <row r="382" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A382" s="3" t="s">
-        <v>359</v>
+        <v>481</v>
       </c>
       <c r="B382" s="3" t="s">
         <v>0</v>
@@ -23370,7 +23361,7 @@
         <v>4</v>
       </c>
       <c r="H382" s="5">
-        <v>175961.76</v>
+        <v>14010.85</v>
       </c>
       <c r="I382" s="4">
         <v>0</v>
@@ -23405,7 +23396,7 @@
     </row>
     <row r="383" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A383" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B383" s="3" t="s">
         <v>0</v>
@@ -23420,13 +23411,13 @@
         <v>3</v>
       </c>
       <c r="F383" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G383" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H383" s="5">
-        <v>86980.72</v>
+        <v>6219.55</v>
       </c>
       <c r="I383" s="4">
         <v>0</v>
@@ -23461,7 +23452,7 @@
     </row>
     <row r="384" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A384" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B384" s="3" t="s">
         <v>0</v>
@@ -23482,7 +23473,7 @@
         <v>4</v>
       </c>
       <c r="H384" s="5">
-        <v>17485.77</v>
+        <v>15125.88</v>
       </c>
       <c r="I384" s="4">
         <v>0</v>
@@ -23517,7 +23508,7 @@
     </row>
     <row r="385" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A385" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B385" s="3" t="s">
         <v>0</v>
@@ -23532,13 +23523,13 @@
         <v>3</v>
       </c>
       <c r="F385" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G385" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H385" s="5">
-        <v>333177.46000000002</v>
+        <v>37440.230000000003</v>
       </c>
       <c r="I385" s="4">
         <v>0</v>
@@ -23573,7 +23564,7 @@
     </row>
     <row r="386" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A386" s="3" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="B386" s="3" t="s">
         <v>0</v>
@@ -23588,13 +23579,13 @@
         <v>3</v>
       </c>
       <c r="F386" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G386" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H386" s="5">
-        <v>54182.879999999997</v>
+        <v>163810.65</v>
       </c>
       <c r="I386" s="4">
         <v>0</v>
@@ -23629,7 +23620,7 @@
     </row>
     <row r="387" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A387" s="3" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
       <c r="B387" s="3" t="s">
         <v>0</v>
@@ -23650,7 +23641,7 @@
         <v>4</v>
       </c>
       <c r="H387" s="5">
-        <v>14010.85</v>
+        <v>27975.63</v>
       </c>
       <c r="I387" s="4">
         <v>0</v>
@@ -23685,7 +23676,7 @@
     </row>
     <row r="388" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A388" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B388" s="3" t="s">
         <v>0</v>
@@ -23700,13 +23691,13 @@
         <v>3</v>
       </c>
       <c r="F388" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G388" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H388" s="5">
-        <v>6219.55</v>
+        <v>105608.58</v>
       </c>
       <c r="I388" s="4">
         <v>0</v>
@@ -23741,7 +23732,7 @@
     </row>
     <row r="389" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A389" s="3" t="s">
-        <v>215</v>
+        <v>422</v>
       </c>
       <c r="B389" s="3" t="s">
         <v>0</v>
@@ -23762,7 +23753,7 @@
         <v>4</v>
       </c>
       <c r="H389" s="5">
-        <v>15125.88</v>
+        <v>64300.17</v>
       </c>
       <c r="I389" s="4">
         <v>0</v>
@@ -23797,7 +23788,7 @@
     </row>
     <row r="390" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A390" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="B390" s="3" t="s">
         <v>0</v>
@@ -23812,13 +23803,13 @@
         <v>3</v>
       </c>
       <c r="F390" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G390" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H390" s="5">
-        <v>37440.230000000003</v>
+        <v>30740.01</v>
       </c>
       <c r="I390" s="4">
         <v>0</v>
@@ -23853,7 +23844,7 @@
     </row>
     <row r="391" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A391" s="3" t="s">
-        <v>217</v>
+        <v>360</v>
       </c>
       <c r="B391" s="3" t="s">
         <v>0</v>
@@ -23868,13 +23859,13 @@
         <v>3</v>
       </c>
       <c r="F391" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G391" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H391" s="5">
-        <v>163810.65</v>
+        <v>71995.649999999994</v>
       </c>
       <c r="I391" s="4">
         <v>0</v>
@@ -23909,7 +23900,7 @@
     </row>
     <row r="392" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A392" s="3" t="s">
-        <v>499</v>
+        <v>220</v>
       </c>
       <c r="B392" s="3" t="s">
         <v>0</v>
@@ -23930,7 +23921,7 @@
         <v>4</v>
       </c>
       <c r="H392" s="5">
-        <v>27975.63</v>
+        <v>4463.5600000000004</v>
       </c>
       <c r="I392" s="4">
         <v>0</v>
@@ -23965,7 +23956,7 @@
     </row>
     <row r="393" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A393" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B393" s="3" t="s">
         <v>0</v>
@@ -23980,13 +23971,13 @@
         <v>3</v>
       </c>
       <c r="F393" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G393" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H393" s="5">
-        <v>105608.58</v>
+        <v>11861.25</v>
       </c>
       <c r="I393" s="4">
         <v>0</v>
@@ -24021,7 +24012,7 @@
     </row>
     <row r="394" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A394" s="3" t="s">
-        <v>422</v>
+        <v>222</v>
       </c>
       <c r="B394" s="3" t="s">
         <v>0</v>
@@ -24042,7 +24033,7 @@
         <v>4</v>
       </c>
       <c r="H394" s="5">
-        <v>64300.17</v>
+        <v>6778.3</v>
       </c>
       <c r="I394" s="4">
         <v>0</v>
@@ -24077,7 +24068,7 @@
     </row>
     <row r="395" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A395" s="3" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B395" s="3" t="s">
         <v>0</v>
@@ -24092,13 +24083,13 @@
         <v>3</v>
       </c>
       <c r="F395" s="4">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G395" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H395" s="5">
-        <v>30740.01</v>
+        <v>125.84</v>
       </c>
       <c r="I395" s="4">
         <v>0</v>
@@ -24133,7 +24124,7 @@
     </row>
     <row r="396" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A396" s="3" t="s">
-        <v>360</v>
+        <v>224</v>
       </c>
       <c r="B396" s="3" t="s">
         <v>0</v>
@@ -24154,7 +24145,7 @@
         <v>4</v>
       </c>
       <c r="H396" s="5">
-        <v>71995.649999999994</v>
+        <v>2207</v>
       </c>
       <c r="I396" s="4">
         <v>0</v>
@@ -24189,7 +24180,7 @@
     </row>
     <row r="397" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A397" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="B397" s="3" t="s">
         <v>0</v>
@@ -24210,7 +24201,7 @@
         <v>4</v>
       </c>
       <c r="H397" s="5">
-        <v>4463.5600000000004</v>
+        <v>2207</v>
       </c>
       <c r="I397" s="4">
         <v>0</v>
@@ -24245,7 +24236,7 @@
     </row>
     <row r="398" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A398" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B398" s="3" t="s">
         <v>0</v>
@@ -24266,7 +24257,7 @@
         <v>4</v>
       </c>
       <c r="H398" s="5">
-        <v>11861.25</v>
+        <v>9995.86</v>
       </c>
       <c r="I398" s="4">
         <v>0</v>
@@ -24301,7 +24292,7 @@
     </row>
     <row r="399" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A399" s="3" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="B399" s="3" t="s">
         <v>0</v>
@@ -24322,7 +24313,7 @@
         <v>4</v>
       </c>
       <c r="H399" s="5">
-        <v>6778.3</v>
+        <v>5587.64</v>
       </c>
       <c r="I399" s="4">
         <v>0</v>
@@ -24357,7 +24348,7 @@
     </row>
     <row r="400" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A400" s="3" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B400" s="3" t="s">
         <v>0</v>
@@ -24372,13 +24363,13 @@
         <v>3</v>
       </c>
       <c r="F400" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G400" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H400" s="5">
-        <v>125.84</v>
+        <v>19127.490000000002</v>
       </c>
       <c r="I400" s="4">
         <v>0</v>
@@ -24413,7 +24404,7 @@
     </row>
     <row r="401" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A401" s="3" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="B401" s="3" t="s">
         <v>0</v>
@@ -24434,7 +24425,7 @@
         <v>4</v>
       </c>
       <c r="H401" s="5">
-        <v>2207</v>
+        <v>48761.68</v>
       </c>
       <c r="I401" s="4">
         <v>0</v>
@@ -24469,7 +24460,7 @@
     </row>
     <row r="402" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A402" s="3" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="B402" s="3" t="s">
         <v>0</v>
@@ -24484,13 +24475,13 @@
         <v>3</v>
       </c>
       <c r="F402" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G402" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H402" s="5">
-        <v>2207</v>
+        <v>34118.080000000002</v>
       </c>
       <c r="I402" s="4">
         <v>0</v>
@@ -24525,7 +24516,7 @@
     </row>
     <row r="403" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A403" s="3" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="B403" s="3" t="s">
         <v>0</v>
@@ -24546,7 +24537,7 @@
         <v>4</v>
       </c>
       <c r="H403" s="5">
-        <v>9995.86</v>
+        <v>28686.84</v>
       </c>
       <c r="I403" s="4">
         <v>0</v>
@@ -24581,7 +24572,7 @@
     </row>
     <row r="404" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A404" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B404" s="3" t="s">
         <v>0</v>
@@ -24602,7 +24593,7 @@
         <v>4</v>
       </c>
       <c r="H404" s="5">
-        <v>5587.64</v>
+        <v>153259.75</v>
       </c>
       <c r="I404" s="4">
         <v>0</v>
@@ -24637,7 +24628,7 @@
     </row>
     <row r="405" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A405" s="3" t="s">
-        <v>227</v>
+        <v>407</v>
       </c>
       <c r="B405" s="3" t="s">
         <v>0</v>
@@ -24658,7 +24649,7 @@
         <v>4</v>
       </c>
       <c r="H405" s="5">
-        <v>19127.490000000002</v>
+        <v>585695.39</v>
       </c>
       <c r="I405" s="4">
         <v>0</v>
@@ -24693,7 +24684,7 @@
     </row>
     <row r="406" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A406" s="3" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="B406" s="3" t="s">
         <v>0</v>
@@ -24714,7 +24705,7 @@
         <v>4</v>
       </c>
       <c r="H406" s="5">
-        <v>48761.68</v>
+        <v>210018.19</v>
       </c>
       <c r="I406" s="4">
         <v>0</v>
@@ -24749,7 +24740,7 @@
     </row>
     <row r="407" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A407" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B407" s="3" t="s">
         <v>0</v>
@@ -24770,7 +24761,7 @@
         <v>4</v>
       </c>
       <c r="H407" s="5">
-        <v>34118.080000000002</v>
+        <v>420036.38</v>
       </c>
       <c r="I407" s="4">
         <v>0</v>
@@ -24805,7 +24796,7 @@
     </row>
     <row r="408" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A408" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="B408" s="3" t="s">
         <v>0</v>
@@ -24826,7 +24817,7 @@
         <v>4</v>
       </c>
       <c r="H408" s="5">
-        <v>28686.84</v>
+        <v>371959.83</v>
       </c>
       <c r="I408" s="4">
         <v>0</v>
@@ -24861,7 +24852,7 @@
     </row>
     <row r="409" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A409" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="B409" s="3" t="s">
         <v>0</v>
@@ -24876,13 +24867,13 @@
         <v>3</v>
       </c>
       <c r="F409" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G409" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H409" s="5">
-        <v>153259.75</v>
+        <v>71070.62</v>
       </c>
       <c r="I409" s="4">
         <v>0</v>
@@ -24917,7 +24908,7 @@
     </row>
     <row r="410" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A410" s="3" t="s">
-        <v>407</v>
+        <v>235</v>
       </c>
       <c r="B410" s="3" t="s">
         <v>0</v>
@@ -24932,13 +24923,13 @@
         <v>3</v>
       </c>
       <c r="F410" s="4">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="G410" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H410" s="5">
-        <v>585695.39</v>
+        <v>18268.63</v>
       </c>
       <c r="I410" s="4">
         <v>0</v>
@@ -24973,7 +24964,7 @@
     </row>
     <row r="411" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A411" s="3" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B411" s="3" t="s">
         <v>0</v>
@@ -24988,13 +24979,13 @@
         <v>3</v>
       </c>
       <c r="F411" s="4">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="G411" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H411" s="5">
-        <v>210018.19</v>
+        <v>9638.27</v>
       </c>
       <c r="I411" s="4">
         <v>0</v>
@@ -25029,7 +25020,7 @@
     </row>
     <row r="412" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A412" s="3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B412" s="3" t="s">
         <v>0</v>
@@ -25044,13 +25035,13 @@
         <v>3</v>
       </c>
       <c r="F412" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G412" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H412" s="5">
-        <v>420036.38</v>
+        <v>22495.01</v>
       </c>
       <c r="I412" s="4">
         <v>0</v>
@@ -25085,7 +25076,7 @@
     </row>
     <row r="413" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A413" s="3" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="B413" s="3" t="s">
         <v>0</v>
@@ -25100,13 +25091,13 @@
         <v>3</v>
       </c>
       <c r="F413" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G413" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H413" s="5">
-        <v>371959.83</v>
+        <v>34114.080000000002</v>
       </c>
       <c r="I413" s="4">
         <v>0</v>
@@ -25141,7 +25132,7 @@
     </row>
     <row r="414" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A414" s="3" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B414" s="3" t="s">
         <v>0</v>
@@ -25156,13 +25147,13 @@
         <v>3</v>
       </c>
       <c r="F414" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G414" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H414" s="5">
-        <v>71070.62</v>
+        <v>60744.480000000003</v>
       </c>
       <c r="I414" s="4">
         <v>0</v>
@@ -25197,7 +25188,7 @@
     </row>
     <row r="415" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A415" s="3" t="s">
-        <v>235</v>
+        <v>474</v>
       </c>
       <c r="B415" s="3" t="s">
         <v>0</v>
@@ -25212,13 +25203,13 @@
         <v>3</v>
       </c>
       <c r="F415" s="4">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="G415" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H415" s="5">
-        <v>18268.63</v>
+        <v>7961.83</v>
       </c>
       <c r="I415" s="4">
         <v>0</v>
@@ -25253,7 +25244,7 @@
     </row>
     <row r="416" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A416" s="3" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="B416" s="3" t="s">
         <v>0</v>
@@ -25268,13 +25259,13 @@
         <v>3</v>
       </c>
       <c r="F416" s="4">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="G416" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H416" s="5">
-        <v>9638.27</v>
+        <v>222168.48</v>
       </c>
       <c r="I416" s="4">
         <v>0</v>
@@ -25309,7 +25300,7 @@
     </row>
     <row r="417" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A417" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="B417" s="3" t="s">
         <v>0</v>
@@ -25324,13 +25315,13 @@
         <v>3</v>
       </c>
       <c r="F417" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G417" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H417" s="5">
-        <v>22495.01</v>
+        <v>222168.48</v>
       </c>
       <c r="I417" s="4">
         <v>0</v>
@@ -25365,7 +25356,7 @@
     </row>
     <row r="418" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A418" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B418" s="3" t="s">
         <v>0</v>
@@ -25380,13 +25371,13 @@
         <v>3</v>
       </c>
       <c r="F418" s="4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G418" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H418" s="5">
-        <v>34114.080000000002</v>
+        <v>0</v>
       </c>
       <c r="I418" s="4">
         <v>0</v>
@@ -25421,7 +25412,7 @@
     </row>
     <row r="419" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A419" s="3" t="s">
-        <v>239</v>
+        <v>367</v>
       </c>
       <c r="B419" s="3" t="s">
         <v>0</v>
@@ -25435,14 +25426,14 @@
       <c r="E419" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F419" s="4">
-        <v>1</v>
+      <c r="F419" s="6">
+        <v>0.2</v>
       </c>
       <c r="G419" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H419" s="5">
-        <v>60744.480000000003</v>
+        <v>179410.69</v>
       </c>
       <c r="I419" s="4">
         <v>0</v>
@@ -25477,7 +25468,7 @@
     </row>
     <row r="420" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A420" s="3" t="s">
-        <v>477</v>
+        <v>242</v>
       </c>
       <c r="B420" s="3" t="s">
         <v>0</v>
@@ -25498,7 +25489,7 @@
         <v>4</v>
       </c>
       <c r="H420" s="5">
-        <v>7961.83</v>
+        <v>177827.97</v>
       </c>
       <c r="I420" s="4">
         <v>0</v>
@@ -25533,7 +25524,7 @@
     </row>
     <row r="421" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A421" s="3" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="B421" s="3" t="s">
         <v>0</v>
@@ -25554,7 +25545,7 @@
         <v>4</v>
       </c>
       <c r="H421" s="5">
-        <v>222168.48</v>
+        <v>123006.3</v>
       </c>
       <c r="I421" s="4">
         <v>0</v>
@@ -25589,7 +25580,7 @@
     </row>
     <row r="422" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A422" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B422" s="3" t="s">
         <v>0</v>
@@ -25604,13 +25595,13 @@
         <v>3</v>
       </c>
       <c r="F422" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G422" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H422" s="5">
-        <v>222168.48</v>
+        <v>47995.199999999997</v>
       </c>
       <c r="I422" s="4">
         <v>0</v>
@@ -25645,7 +25636,7 @@
     </row>
     <row r="423" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A423" s="3" t="s">
-        <v>241</v>
+        <v>408</v>
       </c>
       <c r="B423" s="3" t="s">
         <v>0</v>
@@ -25657,10 +25648,10 @@
         <v>2</v>
       </c>
       <c r="E423" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F423" s="4">
-        <v>2</v>
+        <v>245</v>
+      </c>
+      <c r="F423" s="6">
+        <v>33.4</v>
       </c>
       <c r="G423" s="3" t="s">
         <v>4</v>
@@ -25701,7 +25692,7 @@
     </row>
     <row r="424" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A424" s="3" t="s">
-        <v>367</v>
+        <v>408</v>
       </c>
       <c r="B424" s="3" t="s">
         <v>0</v>
@@ -25713,16 +25704,16 @@
         <v>2</v>
       </c>
       <c r="E424" s="3" t="s">
-        <v>3</v>
+        <v>245</v>
       </c>
       <c r="F424" s="6">
-        <v>0.2</v>
+        <v>2.4900000000000002</v>
       </c>
       <c r="G424" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H424" s="5">
-        <v>260950.96</v>
+        <v>0</v>
       </c>
       <c r="I424" s="4">
         <v>0</v>
@@ -25757,7 +25748,7 @@
     </row>
     <row r="425" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A425" s="3" t="s">
-        <v>242</v>
+        <v>408</v>
       </c>
       <c r="B425" s="3" t="s">
         <v>0</v>
@@ -25769,16 +25760,16 @@
         <v>2</v>
       </c>
       <c r="E425" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F425" s="4">
-        <v>1</v>
+        <v>245</v>
+      </c>
+      <c r="F425" s="6">
+        <v>33.28</v>
       </c>
       <c r="G425" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H425" s="5">
-        <v>177827.97</v>
+        <v>0</v>
       </c>
       <c r="I425" s="4">
         <v>0</v>
@@ -25813,7 +25804,7 @@
     </row>
     <row r="426" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A426" s="3" t="s">
-        <v>243</v>
+        <v>408</v>
       </c>
       <c r="B426" s="3" t="s">
         <v>0</v>
@@ -25825,16 +25816,16 @@
         <v>2</v>
       </c>
       <c r="E426" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F426" s="4">
-        <v>1</v>
+        <v>245</v>
+      </c>
+      <c r="F426" s="6">
+        <v>36.29</v>
       </c>
       <c r="G426" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H426" s="5">
-        <v>123006.3</v>
+        <v>0</v>
       </c>
       <c r="I426" s="4">
         <v>0</v>
@@ -25869,7 +25860,7 @@
     </row>
     <row r="427" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A427" s="3" t="s">
-        <v>244</v>
+        <v>408</v>
       </c>
       <c r="B427" s="3" t="s">
         <v>0</v>
@@ -25881,16 +25872,16 @@
         <v>2</v>
       </c>
       <c r="E427" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F427" s="4">
-        <v>4</v>
+        <v>245</v>
+      </c>
+      <c r="F427" s="6">
+        <v>33.229999999999997</v>
       </c>
       <c r="G427" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H427" s="5">
-        <v>47995.199999999997</v>
+        <v>0</v>
       </c>
       <c r="I427" s="4">
         <v>0</v>
@@ -25940,7 +25931,7 @@
         <v>245</v>
       </c>
       <c r="F428" s="6">
-        <v>33.4</v>
+        <v>35.090000000000003</v>
       </c>
       <c r="G428" s="3" t="s">
         <v>4</v>
@@ -25996,7 +25987,7 @@
         <v>245</v>
       </c>
       <c r="F429" s="6">
-        <v>2.4900000000000002</v>
+        <v>33.26</v>
       </c>
       <c r="G429" s="3" t="s">
         <v>4</v>
@@ -26052,7 +26043,7 @@
         <v>245</v>
       </c>
       <c r="F430" s="6">
-        <v>33.28</v>
+        <v>35.130000000000003</v>
       </c>
       <c r="G430" s="3" t="s">
         <v>4</v>
@@ -26108,7 +26099,7 @@
         <v>245</v>
       </c>
       <c r="F431" s="6">
-        <v>36.29</v>
+        <v>29.77</v>
       </c>
       <c r="G431" s="3" t="s">
         <v>4</v>
@@ -26164,7 +26155,7 @@
         <v>245</v>
       </c>
       <c r="F432" s="6">
-        <v>33.229999999999997</v>
+        <v>35.74</v>
       </c>
       <c r="G432" s="3" t="s">
         <v>4</v>
@@ -26205,7 +26196,7 @@
     </row>
     <row r="433" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A433" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B433" s="3" t="s">
         <v>0</v>
@@ -26220,7 +26211,7 @@
         <v>245</v>
       </c>
       <c r="F433" s="6">
-        <v>35.090000000000003</v>
+        <v>35.06</v>
       </c>
       <c r="G433" s="3" t="s">
         <v>4</v>
@@ -26261,7 +26252,7 @@
     </row>
     <row r="434" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A434" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B434" s="3" t="s">
         <v>0</v>
@@ -26276,7 +26267,7 @@
         <v>245</v>
       </c>
       <c r="F434" s="6">
-        <v>33.26</v>
+        <v>36.36</v>
       </c>
       <c r="G434" s="3" t="s">
         <v>4</v>
@@ -26317,7 +26308,7 @@
     </row>
     <row r="435" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A435" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B435" s="3" t="s">
         <v>0</v>
@@ -26332,7 +26323,7 @@
         <v>245</v>
       </c>
       <c r="F435" s="6">
-        <v>35.130000000000003</v>
+        <v>34.85</v>
       </c>
       <c r="G435" s="3" t="s">
         <v>4</v>
@@ -26373,7 +26364,7 @@
     </row>
     <row r="436" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A436" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B436" s="3" t="s">
         <v>0</v>
@@ -26388,7 +26379,7 @@
         <v>245</v>
       </c>
       <c r="F436" s="6">
-        <v>29.77</v>
+        <v>29.95</v>
       </c>
       <c r="G436" s="3" t="s">
         <v>4</v>
@@ -26429,7 +26420,7 @@
     </row>
     <row r="437" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A437" s="3" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B437" s="3" t="s">
         <v>0</v>
@@ -26444,7 +26435,7 @@
         <v>245</v>
       </c>
       <c r="F437" s="6">
-        <v>35.74</v>
+        <v>29.21</v>
       </c>
       <c r="G437" s="3" t="s">
         <v>4</v>
@@ -26500,7 +26491,7 @@
         <v>245</v>
       </c>
       <c r="F438" s="6">
-        <v>35.06</v>
+        <v>33.409999999999997</v>
       </c>
       <c r="G438" s="3" t="s">
         <v>4</v>
@@ -26556,7 +26547,7 @@
         <v>245</v>
       </c>
       <c r="F439" s="6">
-        <v>36.36</v>
+        <v>35.950000000000003</v>
       </c>
       <c r="G439" s="3" t="s">
         <v>4</v>
@@ -26612,7 +26603,7 @@
         <v>245</v>
       </c>
       <c r="F440" s="6">
-        <v>34.85</v>
+        <v>32.409999999999997</v>
       </c>
       <c r="G440" s="3" t="s">
         <v>4</v>
@@ -26668,7 +26659,7 @@
         <v>245</v>
       </c>
       <c r="F441" s="6">
-        <v>29.95</v>
+        <v>30.44</v>
       </c>
       <c r="G441" s="3" t="s">
         <v>4</v>
@@ -26709,7 +26700,7 @@
     </row>
     <row r="442" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A442" s="3" t="s">
-        <v>409</v>
+        <v>497</v>
       </c>
       <c r="B442" s="3" t="s">
         <v>0</v>
@@ -26724,7 +26715,7 @@
         <v>245</v>
       </c>
       <c r="F442" s="6">
-        <v>29.21</v>
+        <v>36.159999999999997</v>
       </c>
       <c r="G442" s="3" t="s">
         <v>4</v>
@@ -26765,7 +26756,7 @@
     </row>
     <row r="443" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A443" s="3" t="s">
-        <v>409</v>
+        <v>497</v>
       </c>
       <c r="B443" s="3" t="s">
         <v>0</v>
@@ -26780,7 +26771,7 @@
         <v>245</v>
       </c>
       <c r="F443" s="6">
-        <v>33.409999999999997</v>
+        <v>34.57</v>
       </c>
       <c r="G443" s="3" t="s">
         <v>4</v>
@@ -26821,7 +26812,7 @@
     </row>
     <row r="444" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A444" s="3" t="s">
-        <v>409</v>
+        <v>497</v>
       </c>
       <c r="B444" s="3" t="s">
         <v>0</v>
@@ -26836,7 +26827,7 @@
         <v>245</v>
       </c>
       <c r="F444" s="6">
-        <v>35.950000000000003</v>
+        <v>34.93</v>
       </c>
       <c r="G444" s="3" t="s">
         <v>4</v>
@@ -26877,7 +26868,7 @@
     </row>
     <row r="445" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A445" s="3" t="s">
-        <v>409</v>
+        <v>497</v>
       </c>
       <c r="B445" s="3" t="s">
         <v>0</v>
@@ -26892,7 +26883,7 @@
         <v>245</v>
       </c>
       <c r="F445" s="6">
-        <v>32.409999999999997</v>
+        <v>36.43</v>
       </c>
       <c r="G445" s="3" t="s">
         <v>4</v>
@@ -26933,7 +26924,7 @@
     </row>
     <row r="446" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A446" s="3" t="s">
-        <v>409</v>
+        <v>497</v>
       </c>
       <c r="B446" s="3" t="s">
         <v>0</v>
@@ -26948,7 +26939,7 @@
         <v>245</v>
       </c>
       <c r="F446" s="6">
-        <v>30.44</v>
+        <v>35.33</v>
       </c>
       <c r="G446" s="3" t="s">
         <v>4</v>
@@ -26989,7 +26980,7 @@
     </row>
     <row r="447" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A447" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B447" s="3" t="s">
         <v>0</v>
@@ -27004,7 +26995,7 @@
         <v>245</v>
       </c>
       <c r="F447" s="6">
-        <v>36.159999999999997</v>
+        <v>35.56</v>
       </c>
       <c r="G447" s="3" t="s">
         <v>4</v>
@@ -27045,7 +27036,7 @@
     </row>
     <row r="448" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A448" s="3" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="B448" s="3" t="s">
         <v>0</v>
@@ -27060,7 +27051,7 @@
         <v>245</v>
       </c>
       <c r="F448" s="6">
-        <v>34.57</v>
+        <v>35.840000000000003</v>
       </c>
       <c r="G448" s="3" t="s">
         <v>4</v>
@@ -27101,7 +27092,7 @@
     </row>
     <row r="449" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A449" s="3" t="s">
-        <v>500</v>
+        <v>452</v>
       </c>
       <c r="B449" s="3" t="s">
         <v>0</v>
@@ -27113,10 +27104,10 @@
         <v>2</v>
       </c>
       <c r="E449" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F449" s="6">
-        <v>34.93</v>
+        <v>453</v>
+      </c>
+      <c r="F449" s="4">
+        <v>105</v>
       </c>
       <c r="G449" s="3" t="s">
         <v>4</v>
@@ -27157,7 +27148,7 @@
     </row>
     <row r="450" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A450" s="3" t="s">
-        <v>500</v>
+        <v>452</v>
       </c>
       <c r="B450" s="3" t="s">
         <v>0</v>
@@ -27169,10 +27160,10 @@
         <v>2</v>
       </c>
       <c r="E450" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F450" s="6">
-        <v>36.43</v>
+        <v>453</v>
+      </c>
+      <c r="F450" s="4">
+        <v>65</v>
       </c>
       <c r="G450" s="3" t="s">
         <v>4</v>
@@ -27213,7 +27204,7 @@
     </row>
     <row r="451" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A451" s="3" t="s">
-        <v>500</v>
+        <v>452</v>
       </c>
       <c r="B451" s="3" t="s">
         <v>0</v>
@@ -27225,10 +27216,10 @@
         <v>2</v>
       </c>
       <c r="E451" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F451" s="6">
-        <v>35.33</v>
+        <v>453</v>
+      </c>
+      <c r="F451" s="4">
+        <v>120</v>
       </c>
       <c r="G451" s="3" t="s">
         <v>4</v>
@@ -27269,7 +27260,7 @@
     </row>
     <row r="452" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A452" s="3" t="s">
-        <v>500</v>
+        <v>452</v>
       </c>
       <c r="B452" s="3" t="s">
         <v>0</v>
@@ -27281,10 +27272,10 @@
         <v>2</v>
       </c>
       <c r="E452" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F452" s="6">
-        <v>35.56</v>
+        <v>453</v>
+      </c>
+      <c r="F452" s="4">
+        <v>105</v>
       </c>
       <c r="G452" s="3" t="s">
         <v>4</v>
@@ -27325,7 +27316,7 @@
     </row>
     <row r="453" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A453" s="3" t="s">
-        <v>452</v>
+        <v>459</v>
       </c>
       <c r="B453" s="3" t="s">
         <v>0</v>
@@ -27337,10 +27328,10 @@
         <v>2</v>
       </c>
       <c r="E453" s="3" t="s">
-        <v>453</v>
+        <v>460</v>
       </c>
       <c r="F453" s="4">
-        <v>105</v>
+        <v>16800</v>
       </c>
       <c r="G453" s="3" t="s">
         <v>4</v>
@@ -27381,7 +27372,7 @@
     </row>
     <row r="454" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A454" s="3" t="s">
-        <v>452</v>
+        <v>247</v>
       </c>
       <c r="B454" s="3" t="s">
         <v>0</v>
@@ -27393,10 +27384,10 @@
         <v>2</v>
       </c>
       <c r="E454" s="3" t="s">
-        <v>453</v>
+        <v>3</v>
       </c>
       <c r="F454" s="4">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="G454" s="3" t="s">
         <v>4</v>
@@ -27437,7 +27428,7 @@
     </row>
     <row r="455" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A455" s="3" t="s">
-        <v>452</v>
+        <v>498</v>
       </c>
       <c r="B455" s="3" t="s">
         <v>0</v>
@@ -27449,10 +27440,10 @@
         <v>2</v>
       </c>
       <c r="E455" s="3" t="s">
-        <v>453</v>
+        <v>3</v>
       </c>
       <c r="F455" s="4">
-        <v>120</v>
+        <v>2</v>
       </c>
       <c r="G455" s="3" t="s">
         <v>4</v>
@@ -27493,7 +27484,7 @@
     </row>
     <row r="456" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A456" s="3" t="s">
-        <v>452</v>
+        <v>499</v>
       </c>
       <c r="B456" s="3" t="s">
         <v>0</v>
@@ -27505,10 +27496,10 @@
         <v>2</v>
       </c>
       <c r="E456" s="3" t="s">
-        <v>453</v>
+        <v>3</v>
       </c>
       <c r="F456" s="4">
-        <v>105</v>
+        <v>4</v>
       </c>
       <c r="G456" s="3" t="s">
         <v>4</v>
@@ -27549,7 +27540,7 @@
     </row>
     <row r="457" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A457" s="3" t="s">
-        <v>459</v>
+        <v>500</v>
       </c>
       <c r="B457" s="3" t="s">
         <v>0</v>
@@ -27561,10 +27552,10 @@
         <v>2</v>
       </c>
       <c r="E457" s="3" t="s">
-        <v>460</v>
+        <v>3</v>
       </c>
       <c r="F457" s="4">
-        <v>16800</v>
+        <v>2</v>
       </c>
       <c r="G457" s="3" t="s">
         <v>4</v>
@@ -27605,7 +27596,7 @@
     </row>
     <row r="458" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A458" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B458" s="3" t="s">
         <v>0</v>
@@ -27661,7 +27652,7 @@
     </row>
     <row r="459" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A459" s="3" t="s">
-        <v>501</v>
+        <v>249</v>
       </c>
       <c r="B459" s="3" t="s">
         <v>0</v>
@@ -27676,7 +27667,7 @@
         <v>3</v>
       </c>
       <c r="F459" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G459" s="3" t="s">
         <v>4</v>
@@ -27717,7 +27708,7 @@
     </row>
     <row r="460" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A460" s="3" t="s">
-        <v>502</v>
+        <v>250</v>
       </c>
       <c r="B460" s="3" t="s">
         <v>0</v>
@@ -27732,7 +27723,7 @@
         <v>3</v>
       </c>
       <c r="F460" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G460" s="3" t="s">
         <v>4</v>
@@ -27773,7 +27764,7 @@
     </row>
     <row r="461" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A461" s="3" t="s">
-        <v>503</v>
+        <v>251</v>
       </c>
       <c r="B461" s="3" t="s">
         <v>0</v>
@@ -27788,7 +27779,7 @@
         <v>3</v>
       </c>
       <c r="F461" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G461" s="3" t="s">
         <v>4</v>
@@ -27829,7 +27820,7 @@
     </row>
     <row r="462" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A462" s="3" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B462" s="3" t="s">
         <v>0</v>
@@ -27885,7 +27876,7 @@
     </row>
     <row r="463" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A463" s="3" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B463" s="3" t="s">
         <v>0</v>
@@ -27900,7 +27891,7 @@
         <v>3</v>
       </c>
       <c r="F463" s="4">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G463" s="3" t="s">
         <v>4</v>
@@ -27941,7 +27932,7 @@
     </row>
     <row r="464" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A464" s="3" t="s">
-        <v>250</v>
+        <v>501</v>
       </c>
       <c r="B464" s="3" t="s">
         <v>0</v>
@@ -27997,7 +27988,7 @@
     </row>
     <row r="465" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A465" s="3" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B465" s="3" t="s">
         <v>0</v>
@@ -28012,7 +28003,7 @@
         <v>3</v>
       </c>
       <c r="F465" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G465" s="3" t="s">
         <v>4</v>
@@ -28053,7 +28044,7 @@
     </row>
     <row r="466" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A466" s="3" t="s">
-        <v>251</v>
+        <v>502</v>
       </c>
       <c r="B466" s="3" t="s">
         <v>0</v>
@@ -28068,7 +28059,7 @@
         <v>3</v>
       </c>
       <c r="F466" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G466" s="3" t="s">
         <v>4</v>
@@ -28109,7 +28100,7 @@
     </row>
     <row r="467" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A467" s="3" t="s">
-        <v>252</v>
+        <v>503</v>
       </c>
       <c r="B467" s="3" t="s">
         <v>0</v>
@@ -28124,7 +28115,7 @@
         <v>3</v>
       </c>
       <c r="F467" s="4">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G467" s="3" t="s">
         <v>4</v>
@@ -28165,7 +28156,7 @@
     </row>
     <row r="468" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A468" s="3" t="s">
-        <v>504</v>
+        <v>254</v>
       </c>
       <c r="B468" s="3" t="s">
         <v>0</v>
@@ -28180,7 +28171,7 @@
         <v>3</v>
       </c>
       <c r="F468" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G468" s="3" t="s">
         <v>4</v>
@@ -28221,7 +28212,7 @@
     </row>
     <row r="469" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A469" s="3" t="s">
-        <v>253</v>
+        <v>423</v>
       </c>
       <c r="B469" s="3" t="s">
         <v>0</v>
@@ -28236,7 +28227,7 @@
         <v>3</v>
       </c>
       <c r="F469" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G469" s="3" t="s">
         <v>4</v>
@@ -28277,7 +28268,7 @@
     </row>
     <row r="470" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A470" s="3" t="s">
-        <v>505</v>
+        <v>424</v>
       </c>
       <c r="B470" s="3" t="s">
         <v>0</v>
@@ -28292,7 +28283,7 @@
         <v>3</v>
       </c>
       <c r="F470" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G470" s="3" t="s">
         <v>4</v>
@@ -28333,7 +28324,7 @@
     </row>
     <row r="471" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A471" s="3" t="s">
-        <v>506</v>
+        <v>425</v>
       </c>
       <c r="B471" s="3" t="s">
         <v>0</v>
@@ -28348,7 +28339,7 @@
         <v>3</v>
       </c>
       <c r="F471" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G471" s="3" t="s">
         <v>4</v>
@@ -28389,7 +28380,7 @@
     </row>
     <row r="472" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A472" s="3" t="s">
-        <v>254</v>
+        <v>426</v>
       </c>
       <c r="B472" s="3" t="s">
         <v>0</v>
@@ -28445,7 +28436,7 @@
     </row>
     <row r="473" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A473" s="3" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B473" s="3" t="s">
         <v>0</v>
@@ -28501,7 +28492,7 @@
     </row>
     <row r="474" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A474" s="3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B474" s="3" t="s">
         <v>0</v>
@@ -28557,7 +28548,7 @@
     </row>
     <row r="475" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A475" s="3" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B475" s="3" t="s">
         <v>0</v>
@@ -28613,7 +28604,7 @@
     </row>
     <row r="476" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A476" s="3" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="B476" s="3" t="s">
         <v>0</v>
@@ -28669,7 +28660,7 @@
     </row>
     <row r="477" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A477" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="B477" s="3" t="s">
         <v>0</v>
@@ -28725,7 +28716,7 @@
     </row>
     <row r="478" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A478" s="3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="B478" s="3" t="s">
         <v>0</v>
@@ -28781,7 +28772,7 @@
     </row>
     <row r="479" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A479" s="3" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="B479" s="3" t="s">
         <v>0</v>
@@ -28837,7 +28828,7 @@
     </row>
     <row r="480" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A480" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="B480" s="3" t="s">
         <v>0</v>
@@ -28893,7 +28884,7 @@
     </row>
     <row r="481" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A481" s="3" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="B481" s="3" t="s">
         <v>0</v>
@@ -28949,7 +28940,7 @@
     </row>
     <row r="482" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A482" s="3" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="B482" s="3" t="s">
         <v>0</v>
@@ -29005,7 +28996,7 @@
     </row>
     <row r="483" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A483" s="3" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="B483" s="3" t="s">
         <v>0</v>
@@ -29061,7 +29052,7 @@
     </row>
     <row r="484" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A484" s="3" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B484" s="3" t="s">
         <v>0</v>
@@ -29117,7 +29108,7 @@
     </row>
     <row r="485" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A485" s="3" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B485" s="3" t="s">
         <v>0</v>
@@ -29173,7 +29164,7 @@
     </row>
     <row r="486" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A486" s="3" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B486" s="3" t="s">
         <v>0</v>
@@ -29229,7 +29220,7 @@
     </row>
     <row r="487" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A487" s="3" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B487" s="3" t="s">
         <v>0</v>
@@ -29285,7 +29276,7 @@
     </row>
     <row r="488" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A488" s="3" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B488" s="3" t="s">
         <v>0</v>
@@ -29341,7 +29332,7 @@
     </row>
     <row r="489" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A489" s="3" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B489" s="3" t="s">
         <v>0</v>
@@ -29397,7 +29388,7 @@
     </row>
     <row r="490" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A490" s="3" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="B490" s="3" t="s">
         <v>0</v>
@@ -29453,7 +29444,7 @@
     </row>
     <row r="491" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A491" s="3" t="s">
-        <v>441</v>
+        <v>486</v>
       </c>
       <c r="B491" s="3" t="s">
         <v>0</v>
@@ -29465,10 +29456,10 @@
         <v>2</v>
       </c>
       <c r="E491" s="3" t="s">
-        <v>3</v>
+        <v>487</v>
       </c>
       <c r="F491" s="4">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="G491" s="3" t="s">
         <v>4</v>
@@ -29509,7 +29500,7 @@
     </row>
     <row r="492" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A492" s="3" t="s">
-        <v>442</v>
+        <v>255</v>
       </c>
       <c r="B492" s="3" t="s">
         <v>0</v>
@@ -29565,7 +29556,7 @@
     </row>
     <row r="493" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A493" s="3" t="s">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="B493" s="3" t="s">
         <v>0</v>
@@ -29621,7 +29612,7 @@
     </row>
     <row r="494" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A494" s="3" t="s">
-        <v>444</v>
+        <v>256</v>
       </c>
       <c r="B494" s="3" t="s">
         <v>0</v>
@@ -29677,7 +29668,7 @@
     </row>
     <row r="495" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A495" s="3" t="s">
-        <v>489</v>
+        <v>445</v>
       </c>
       <c r="B495" s="3" t="s">
         <v>0</v>
@@ -29689,10 +29680,10 @@
         <v>2</v>
       </c>
       <c r="E495" s="3" t="s">
-        <v>490</v>
+        <v>3</v>
       </c>
       <c r="F495" s="4">
-        <v>100</v>
+        <v>4</v>
       </c>
       <c r="G495" s="3" t="s">
         <v>4</v>
@@ -29733,7 +29724,7 @@
     </row>
     <row r="496" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A496" s="3" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B496" s="3" t="s">
         <v>0</v>
@@ -29748,7 +29739,7 @@
         <v>3</v>
       </c>
       <c r="F496" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G496" s="3" t="s">
         <v>4</v>
@@ -29789,7 +29780,7 @@
     </row>
     <row r="497" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A497" s="3" t="s">
-        <v>456</v>
+        <v>392</v>
       </c>
       <c r="B497" s="3" t="s">
         <v>0</v>
@@ -29845,7 +29836,7 @@
     </row>
     <row r="498" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A498" s="3" t="s">
-        <v>256</v>
+        <v>392</v>
       </c>
       <c r="B498" s="3" t="s">
         <v>0</v>
@@ -29860,7 +29851,7 @@
         <v>3</v>
       </c>
       <c r="F498" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G498" s="3" t="s">
         <v>4</v>
@@ -29901,7 +29892,7 @@
     </row>
     <row r="499" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A499" s="3" t="s">
-        <v>445</v>
+        <v>258</v>
       </c>
       <c r="B499" s="3" t="s">
         <v>0</v>
@@ -29957,7 +29948,7 @@
     </row>
     <row r="500" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A500" s="3" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B500" s="3" t="s">
         <v>0</v>
@@ -29972,7 +29963,7 @@
         <v>3</v>
       </c>
       <c r="F500" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G500" s="3" t="s">
         <v>4</v>
@@ -30013,7 +30004,7 @@
     </row>
     <row r="501" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A501" s="3" t="s">
-        <v>392</v>
+        <v>410</v>
       </c>
       <c r="B501" s="3" t="s">
         <v>0</v>
@@ -30028,7 +30019,7 @@
         <v>3</v>
       </c>
       <c r="F501" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G501" s="3" t="s">
         <v>4</v>
@@ -30069,7 +30060,7 @@
     </row>
     <row r="502" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A502" s="3" t="s">
-        <v>392</v>
+        <v>259</v>
       </c>
       <c r="B502" s="3" t="s">
         <v>0</v>
@@ -30081,10 +30072,10 @@
         <v>2</v>
       </c>
       <c r="E502" s="3" t="s">
-        <v>3</v>
+        <v>246</v>
       </c>
       <c r="F502" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G502" s="3" t="s">
         <v>4</v>
@@ -30111,7 +30102,7 @@
         <v>0</v>
       </c>
       <c r="O502" s="4">
-        <v>0</v>
+        <v>13520</v>
       </c>
       <c r="P502" s="5">
         <v>0</v>
@@ -30125,7 +30116,7 @@
     </row>
     <row r="503" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A503" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B503" s="3" t="s">
         <v>0</v>
@@ -30137,10 +30128,10 @@
         <v>2</v>
       </c>
       <c r="E503" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F503" s="4">
-        <v>4</v>
+        <v>245</v>
+      </c>
+      <c r="F503" s="6">
+        <v>28.6</v>
       </c>
       <c r="G503" s="3" t="s">
         <v>4</v>
@@ -30181,7 +30172,7 @@
     </row>
     <row r="504" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A504" s="3" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="B504" s="3" t="s">
         <v>0</v>
@@ -30193,10 +30184,10 @@
         <v>2</v>
       </c>
       <c r="E504" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F504" s="4">
-        <v>4</v>
+        <v>245</v>
+      </c>
+      <c r="F504" s="6">
+        <v>31.58</v>
       </c>
       <c r="G504" s="3" t="s">
         <v>4</v>
@@ -30237,7 +30228,7 @@
     </row>
     <row r="505" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A505" s="3" t="s">
-        <v>410</v>
+        <v>260</v>
       </c>
       <c r="B505" s="3" t="s">
         <v>0</v>
@@ -30249,10 +30240,10 @@
         <v>2</v>
       </c>
       <c r="E505" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F505" s="4">
-        <v>4</v>
+        <v>245</v>
+      </c>
+      <c r="F505" s="6">
+        <v>33.44</v>
       </c>
       <c r="G505" s="3" t="s">
         <v>4</v>
@@ -30293,7 +30284,7 @@
     </row>
     <row r="506" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A506" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B506" s="3" t="s">
         <v>0</v>
@@ -30305,10 +30296,10 @@
         <v>2</v>
       </c>
       <c r="E506" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="F506" s="4">
-        <v>0</v>
+        <v>245</v>
+      </c>
+      <c r="F506" s="6">
+        <v>31.38</v>
       </c>
       <c r="G506" s="3" t="s">
         <v>4</v>
@@ -30335,7 +30326,7 @@
         <v>0</v>
       </c>
       <c r="O506" s="4">
-        <v>13520</v>
+        <v>0</v>
       </c>
       <c r="P506" s="5">
         <v>0</v>
@@ -30363,8 +30354,8 @@
       <c r="E507" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F507" s="6">
-        <v>28.6</v>
+      <c r="F507" s="4">
+        <v>18</v>
       </c>
       <c r="G507" s="3" t="s">
         <v>4</v>
@@ -30420,7 +30411,7 @@
         <v>245</v>
       </c>
       <c r="F508" s="6">
-        <v>31.58</v>
+        <v>23.6</v>
       </c>
       <c r="G508" s="3" t="s">
         <v>4</v>
@@ -30476,7 +30467,7 @@
         <v>245</v>
       </c>
       <c r="F509" s="6">
-        <v>33.44</v>
+        <v>27.06</v>
       </c>
       <c r="G509" s="3" t="s">
         <v>4</v>
@@ -30532,7 +30523,7 @@
         <v>245</v>
       </c>
       <c r="F510" s="6">
-        <v>31.38</v>
+        <v>36.4</v>
       </c>
       <c r="G510" s="3" t="s">
         <v>4</v>
@@ -30587,8 +30578,8 @@
       <c r="E511" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F511" s="4">
-        <v>18</v>
+      <c r="F511" s="6">
+        <v>28.4</v>
       </c>
       <c r="G511" s="3" t="s">
         <v>4</v>
@@ -30644,7 +30635,7 @@
         <v>245</v>
       </c>
       <c r="F512" s="6">
-        <v>23.6</v>
+        <v>37.74</v>
       </c>
       <c r="G512" s="3" t="s">
         <v>4</v>
@@ -30700,7 +30691,7 @@
         <v>245</v>
       </c>
       <c r="F513" s="6">
-        <v>27.06</v>
+        <v>34.6</v>
       </c>
       <c r="G513" s="3" t="s">
         <v>4</v>
@@ -30756,7 +30747,7 @@
         <v>245</v>
       </c>
       <c r="F514" s="6">
-        <v>36.4</v>
+        <v>28.92</v>
       </c>
       <c r="G514" s="3" t="s">
         <v>4</v>
@@ -30812,7 +30803,7 @@
         <v>245</v>
       </c>
       <c r="F515" s="6">
-        <v>28.4</v>
+        <v>28.68</v>
       </c>
       <c r="G515" s="3" t="s">
         <v>4</v>
@@ -30868,7 +30859,7 @@
         <v>245</v>
       </c>
       <c r="F516" s="6">
-        <v>37.74</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="G516" s="3" t="s">
         <v>4</v>
@@ -30924,7 +30915,7 @@
         <v>245</v>
       </c>
       <c r="F517" s="6">
-        <v>34.6</v>
+        <v>25.32</v>
       </c>
       <c r="G517" s="3" t="s">
         <v>4</v>
@@ -30980,7 +30971,7 @@
         <v>245</v>
       </c>
       <c r="F518" s="6">
-        <v>28.92</v>
+        <v>27.64</v>
       </c>
       <c r="G518" s="3" t="s">
         <v>4</v>
@@ -31021,7 +31012,7 @@
     </row>
     <row r="519" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A519" s="3" t="s">
-        <v>260</v>
+        <v>471</v>
       </c>
       <c r="B519" s="3" t="s">
         <v>0</v>
@@ -31033,10 +31024,10 @@
         <v>2</v>
       </c>
       <c r="E519" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F519" s="6">
-        <v>28.68</v>
+        <v>3</v>
+      </c>
+      <c r="F519" s="4">
+        <v>1170</v>
       </c>
       <c r="G519" s="3" t="s">
         <v>4</v>
@@ -31077,7 +31068,7 @@
     </row>
     <row r="520" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A520" s="3" t="s">
-        <v>260</v>
+        <v>457</v>
       </c>
       <c r="B520" s="3" t="s">
         <v>0</v>
@@ -31089,10 +31080,10 @@
         <v>2</v>
       </c>
       <c r="E520" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F520" s="6">
-        <v>2.2000000000000002</v>
+        <v>453</v>
+      </c>
+      <c r="F520" s="4">
+        <v>1</v>
       </c>
       <c r="G520" s="3" t="s">
         <v>4</v>
@@ -31133,7 +31124,7 @@
     </row>
     <row r="521" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A521" s="3" t="s">
-        <v>260</v>
+        <v>457</v>
       </c>
       <c r="B521" s="3" t="s">
         <v>0</v>
@@ -31145,10 +31136,10 @@
         <v>2</v>
       </c>
       <c r="E521" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F521" s="6">
-        <v>25.32</v>
+        <v>453</v>
+      </c>
+      <c r="F521" s="4">
+        <v>1</v>
       </c>
       <c r="G521" s="3" t="s">
         <v>4</v>
@@ -31189,7 +31180,7 @@
     </row>
     <row r="522" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A522" s="3" t="s">
-        <v>260</v>
+        <v>457</v>
       </c>
       <c r="B522" s="3" t="s">
         <v>0</v>
@@ -31201,10 +31192,10 @@
         <v>2</v>
       </c>
       <c r="E522" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F522" s="6">
-        <v>27.64</v>
+        <v>453</v>
+      </c>
+      <c r="F522" s="4">
+        <v>1</v>
       </c>
       <c r="G522" s="3" t="s">
         <v>4</v>
@@ -31245,7 +31236,7 @@
     </row>
     <row r="523" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A523" s="3" t="s">
-        <v>471</v>
+        <v>457</v>
       </c>
       <c r="B523" s="3" t="s">
         <v>0</v>
@@ -31257,10 +31248,10 @@
         <v>2</v>
       </c>
       <c r="E523" s="3" t="s">
-        <v>3</v>
+        <v>453</v>
       </c>
       <c r="F523" s="4">
-        <v>1170</v>
+        <v>1</v>
       </c>
       <c r="G523" s="3" t="s">
         <v>4</v>
@@ -31469,7 +31460,7 @@
     </row>
     <row r="527" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A527" s="3" t="s">
-        <v>457</v>
+        <v>262</v>
       </c>
       <c r="B527" s="3" t="s">
         <v>0</v>
@@ -31481,7 +31472,7 @@
         <v>2</v>
       </c>
       <c r="E527" s="3" t="s">
-        <v>453</v>
+        <v>3</v>
       </c>
       <c r="F527" s="4">
         <v>1</v>
@@ -31525,7 +31516,7 @@
     </row>
     <row r="528" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A528" s="3" t="s">
-        <v>457</v>
+        <v>263</v>
       </c>
       <c r="B528" s="3" t="s">
         <v>0</v>
@@ -31537,7 +31528,7 @@
         <v>2</v>
       </c>
       <c r="E528" s="3" t="s">
-        <v>453</v>
+        <v>3</v>
       </c>
       <c r="F528" s="4">
         <v>1</v>
@@ -31581,7 +31572,7 @@
     </row>
     <row r="529" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A529" s="3" t="s">
-        <v>457</v>
+        <v>264</v>
       </c>
       <c r="B529" s="3" t="s">
         <v>0</v>
@@ -31593,10 +31584,10 @@
         <v>2</v>
       </c>
       <c r="E529" s="3" t="s">
-        <v>453</v>
+        <v>3</v>
       </c>
       <c r="F529" s="4">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G529" s="3" t="s">
         <v>4</v>
@@ -31637,7 +31628,7 @@
     </row>
     <row r="530" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A530" s="3" t="s">
-        <v>262</v>
+        <v>355</v>
       </c>
       <c r="B530" s="3" t="s">
         <v>0</v>
@@ -31658,7 +31649,7 @@
         <v>4</v>
       </c>
       <c r="H530" s="5">
-        <v>0</v>
+        <v>3960938.83</v>
       </c>
       <c r="I530" s="4">
         <v>0</v>
@@ -31693,7 +31684,7 @@
     </row>
     <row r="531" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A531" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B531" s="3" t="s">
         <v>0</v>
@@ -31708,13 +31699,13 @@
         <v>3</v>
       </c>
       <c r="F531" s="4">
-        <v>1</v>
+        <v>14100</v>
       </c>
       <c r="G531" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H531" s="5">
-        <v>0</v>
+        <v>25831206.109999999</v>
       </c>
       <c r="I531" s="4">
         <v>0</v>
@@ -31749,7 +31740,7 @@
     </row>
     <row r="532" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A532" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B532" s="3" t="s">
         <v>0</v>
@@ -31764,13 +31755,13 @@
         <v>3</v>
       </c>
       <c r="F532" s="4">
-        <v>15</v>
+        <v>36000</v>
       </c>
       <c r="G532" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H532" s="5">
-        <v>0</v>
+        <v>65952015.609999999</v>
       </c>
       <c r="I532" s="4">
         <v>0</v>
@@ -31805,7 +31796,7 @@
     </row>
     <row r="533" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A533" s="3" t="s">
-        <v>355</v>
+        <v>482</v>
       </c>
       <c r="B533" s="3" t="s">
         <v>0</v>
@@ -31826,7 +31817,7 @@
         <v>4</v>
       </c>
       <c r="H533" s="5">
-        <v>3960938.83</v>
+        <v>0</v>
       </c>
       <c r="I533" s="4">
         <v>0</v>
@@ -31861,7 +31852,7 @@
     </row>
     <row r="534" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A534" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B534" s="3" t="s">
         <v>0</v>
@@ -31876,13 +31867,13 @@
         <v>3</v>
       </c>
       <c r="F534" s="4">
-        <v>14100</v>
+        <v>1</v>
       </c>
       <c r="G534" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H534" s="5">
-        <v>25050738.359999999</v>
+        <v>13075.98</v>
       </c>
       <c r="I534" s="4">
         <v>0</v>
@@ -31917,7 +31908,7 @@
     </row>
     <row r="535" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A535" s="3" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B535" s="3" t="s">
         <v>0</v>
@@ -31929,16 +31920,16 @@
         <v>2</v>
       </c>
       <c r="E535" s="3" t="s">
-        <v>3</v>
+        <v>245</v>
       </c>
       <c r="F535" s="4">
-        <v>36000</v>
+        <v>24</v>
       </c>
       <c r="G535" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H535" s="5">
-        <v>63959332</v>
+        <v>307304.15999999997</v>
       </c>
       <c r="I535" s="4">
         <v>0</v>
@@ -31973,7 +31964,7 @@
     </row>
     <row r="536" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A536" s="3" t="s">
-        <v>485</v>
+        <v>267</v>
       </c>
       <c r="B536" s="3" t="s">
         <v>0</v>
@@ -31985,16 +31976,16 @@
         <v>2</v>
       </c>
       <c r="E536" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F536" s="4">
-        <v>1</v>
+        <v>245</v>
+      </c>
+      <c r="F536" s="6">
+        <v>27.3</v>
       </c>
       <c r="G536" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H536" s="5">
-        <v>0</v>
+        <v>6453726.9199999999</v>
       </c>
       <c r="I536" s="4">
         <v>0</v>
@@ -32029,7 +32020,7 @@
     </row>
     <row r="537" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A537" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B537" s="3" t="s">
         <v>0</v>
@@ -32041,16 +32032,16 @@
         <v>2</v>
       </c>
       <c r="E537" s="3" t="s">
-        <v>3</v>
+        <v>245</v>
       </c>
       <c r="F537" s="4">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="G537" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H537" s="5">
-        <v>13075.98</v>
+        <v>5910006.3399999999</v>
       </c>
       <c r="I537" s="4">
         <v>0</v>
@@ -32099,14 +32090,14 @@
       <c r="E538" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F538" s="4">
-        <v>24</v>
+      <c r="F538" s="6">
+        <v>24.54</v>
       </c>
       <c r="G538" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H538" s="5">
-        <v>307304.15999999997</v>
+        <v>5801262.2199999997</v>
       </c>
       <c r="I538" s="4">
         <v>0</v>
@@ -32156,13 +32147,13 @@
         <v>245</v>
       </c>
       <c r="F539" s="6">
-        <v>27.3</v>
+        <v>28.72</v>
       </c>
       <c r="G539" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H539" s="5">
-        <v>6453726.9199999999</v>
+        <v>6789415.2800000003</v>
       </c>
       <c r="I539" s="4">
         <v>0</v>
@@ -32212,13 +32203,13 @@
         <v>245</v>
       </c>
       <c r="F540" s="4">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G540" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H540" s="5">
-        <v>5910006.3399999999</v>
+        <v>5200805.58</v>
       </c>
       <c r="I540" s="4">
         <v>0</v>
@@ -32268,13 +32259,13 @@
         <v>245</v>
       </c>
       <c r="F541" s="6">
-        <v>24.54</v>
+        <v>25.64</v>
       </c>
       <c r="G541" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H541" s="5">
-        <v>5801262.2199999997</v>
+        <v>6061302.5</v>
       </c>
       <c r="I541" s="4">
         <v>0</v>
@@ -32324,13 +32315,13 @@
         <v>245</v>
       </c>
       <c r="F542" s="6">
-        <v>28.72</v>
+        <v>27.02</v>
       </c>
       <c r="G542" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H542" s="5">
-        <v>6789415.2800000003</v>
+        <v>6387534.8499999996</v>
       </c>
       <c r="I542" s="4">
         <v>0</v>
@@ -32379,14 +32370,14 @@
       <c r="E543" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F543" s="4">
-        <v>22</v>
+      <c r="F543" s="6">
+        <v>25.72</v>
       </c>
       <c r="G543" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H543" s="5">
-        <v>5200805.58</v>
+        <v>6080214.5199999996</v>
       </c>
       <c r="I543" s="4">
         <v>0</v>
@@ -32436,13 +32427,13 @@
         <v>245</v>
       </c>
       <c r="F544" s="6">
-        <v>25.64</v>
+        <v>26.66</v>
       </c>
       <c r="G544" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H544" s="5">
-        <v>6061302.5</v>
+        <v>6302430.7599999998</v>
       </c>
       <c r="I544" s="4">
         <v>0</v>
@@ -32491,14 +32482,14 @@
       <c r="E545" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F545" s="6">
-        <v>27.02</v>
+      <c r="F545" s="4">
+        <v>27</v>
       </c>
       <c r="G545" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H545" s="5">
-        <v>6387534.8499999996</v>
+        <v>6382806.8499999996</v>
       </c>
       <c r="I545" s="4">
         <v>0</v>
@@ -32548,13 +32539,13 @@
         <v>245</v>
       </c>
       <c r="F546" s="6">
-        <v>25.72</v>
+        <v>13.2</v>
       </c>
       <c r="G546" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H546" s="5">
-        <v>6080214.5199999996</v>
+        <v>3120483.35</v>
       </c>
       <c r="I546" s="4">
         <v>0</v>
@@ -32604,13 +32595,13 @@
         <v>245</v>
       </c>
       <c r="F547" s="6">
-        <v>26.66</v>
+        <v>27.06</v>
       </c>
       <c r="G547" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H547" s="5">
-        <v>6302430.7599999998</v>
+        <v>6396990.8600000003</v>
       </c>
       <c r="I547" s="4">
         <v>0</v>
@@ -32659,14 +32650,14 @@
       <c r="E548" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F548" s="4">
-        <v>27</v>
+      <c r="F548" s="6">
+        <v>0.14000000000000001</v>
       </c>
       <c r="G548" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H548" s="5">
-        <v>6382806.8499999996</v>
+        <v>33096.04</v>
       </c>
       <c r="I548" s="4">
         <v>0</v>
@@ -32716,13 +32707,13 @@
         <v>245</v>
       </c>
       <c r="F549" s="6">
-        <v>13.2</v>
+        <v>15.32</v>
       </c>
       <c r="G549" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H549" s="5">
-        <v>3120483.35</v>
+        <v>3632890.09</v>
       </c>
       <c r="I549" s="4">
         <v>0</v>
@@ -32772,13 +32763,13 @@
         <v>245</v>
       </c>
       <c r="F550" s="6">
-        <v>27.06</v>
+        <v>28.6</v>
       </c>
       <c r="G550" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H550" s="5">
-        <v>6396990.8600000003</v>
+        <v>6782027.1900000004</v>
       </c>
       <c r="I550" s="4">
         <v>0</v>
@@ -32828,13 +32819,13 @@
         <v>245</v>
       </c>
       <c r="F551" s="6">
-        <v>0.14000000000000001</v>
+        <v>29.06</v>
       </c>
       <c r="G551" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H551" s="5">
-        <v>33096.04</v>
+        <v>6891108.75</v>
       </c>
       <c r="I551" s="4">
         <v>0</v>
@@ -32884,13 +32875,13 @@
         <v>245</v>
       </c>
       <c r="F552" s="6">
-        <v>15.32</v>
+        <v>28.08</v>
       </c>
       <c r="G552" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H552" s="5">
-        <v>3632890.09</v>
+        <v>6658717.5999999996</v>
       </c>
       <c r="I552" s="4">
         <v>0</v>
@@ -32940,13 +32931,13 @@
         <v>245</v>
       </c>
       <c r="F553" s="6">
-        <v>28.6</v>
+        <v>29.36</v>
       </c>
       <c r="G553" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H553" s="5">
-        <v>6782027.1900000004</v>
+        <v>6962248.8899999997</v>
       </c>
       <c r="I553" s="4">
         <v>0</v>
@@ -32996,13 +32987,13 @@
         <v>245</v>
       </c>
       <c r="F554" s="6">
-        <v>29.06</v>
+        <v>28.82</v>
       </c>
       <c r="G554" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H554" s="5">
-        <v>6891108.75</v>
+        <v>6834196.6299999999</v>
       </c>
       <c r="I554" s="4">
         <v>0</v>
@@ -33052,13 +33043,13 @@
         <v>245</v>
       </c>
       <c r="F555" s="6">
-        <v>28.08</v>
+        <v>26.62</v>
       </c>
       <c r="G555" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H555" s="5">
-        <v>6658717.5999999996</v>
+        <v>6312502.2300000004</v>
       </c>
       <c r="I555" s="4">
         <v>0</v>
@@ -33108,13 +33099,13 @@
         <v>245</v>
       </c>
       <c r="F556" s="6">
-        <v>29.36</v>
+        <v>25.5</v>
       </c>
       <c r="G556" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H556" s="5">
-        <v>6962248.8899999997</v>
+        <v>6046912.3499999996</v>
       </c>
       <c r="I556" s="4">
         <v>0</v>
@@ -33164,13 +33155,13 @@
         <v>245</v>
       </c>
       <c r="F557" s="6">
-        <v>28.82</v>
+        <v>2.46</v>
       </c>
       <c r="G557" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H557" s="5">
-        <v>6834196.6299999999</v>
+        <v>583349.18999999994</v>
       </c>
       <c r="I557" s="4">
         <v>0</v>
@@ -33220,13 +33211,13 @@
         <v>245</v>
       </c>
       <c r="F558" s="6">
-        <v>26.62</v>
+        <v>6.5</v>
       </c>
       <c r="G558" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H558" s="5">
-        <v>6312502.2300000004</v>
+        <v>1541369.82</v>
       </c>
       <c r="I558" s="4">
         <v>0</v>
@@ -33276,13 +33267,13 @@
         <v>245</v>
       </c>
       <c r="F559" s="6">
-        <v>25.5</v>
+        <v>2.76</v>
       </c>
       <c r="G559" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H559" s="5">
-        <v>6046912.3499999996</v>
+        <v>654489.34</v>
       </c>
       <c r="I559" s="4">
         <v>0</v>
@@ -33332,13 +33323,13 @@
         <v>245</v>
       </c>
       <c r="F560" s="6">
-        <v>2.46</v>
+        <v>1.28</v>
       </c>
       <c r="G560" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H560" s="5">
-        <v>583349.18999999994</v>
+        <v>303531.28999999998</v>
       </c>
       <c r="I560" s="4">
         <v>0</v>
@@ -33388,13 +33379,13 @@
         <v>245</v>
       </c>
       <c r="F561" s="6">
-        <v>6.5</v>
+        <v>18.96</v>
       </c>
       <c r="G561" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H561" s="5">
-        <v>1541369.82</v>
+        <v>4496057.1900000004</v>
       </c>
       <c r="I561" s="4">
         <v>0</v>
@@ -33444,13 +33435,13 @@
         <v>245</v>
       </c>
       <c r="F562" s="6">
-        <v>2.76</v>
+        <v>26.2</v>
       </c>
       <c r="G562" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H562" s="5">
-        <v>654489.34</v>
+        <v>6212906.0300000003</v>
       </c>
       <c r="I562" s="4">
         <v>0</v>
@@ -33499,14 +33490,14 @@
       <c r="E563" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F563" s="6">
-        <v>1.28</v>
+      <c r="F563" s="4">
+        <v>27</v>
       </c>
       <c r="G563" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H563" s="5">
-        <v>303531.28999999998</v>
+        <v>6402613.0800000001</v>
       </c>
       <c r="I563" s="4">
         <v>0</v>
@@ -33556,13 +33547,13 @@
         <v>245</v>
       </c>
       <c r="F564" s="6">
-        <v>18.96</v>
+        <v>26.7</v>
       </c>
       <c r="G564" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H564" s="5">
-        <v>4496057.1900000004</v>
+        <v>6331472.9400000004</v>
       </c>
       <c r="I564" s="4">
         <v>0</v>
@@ -33612,13 +33603,13 @@
         <v>245</v>
       </c>
       <c r="F565" s="6">
-        <v>26.2</v>
+        <v>25.3</v>
       </c>
       <c r="G565" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H565" s="5">
-        <v>6212906.0300000003</v>
+        <v>5999485.5899999999</v>
       </c>
       <c r="I565" s="4">
         <v>0</v>
@@ -33667,14 +33658,14 @@
       <c r="E566" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F566" s="4">
-        <v>27</v>
+      <c r="F566" s="6">
+        <v>25.7</v>
       </c>
       <c r="G566" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H566" s="5">
-        <v>6402613.0800000001</v>
+        <v>6094339.1200000001</v>
       </c>
       <c r="I566" s="4">
         <v>0</v>
@@ -33724,13 +33715,13 @@
         <v>245</v>
       </c>
       <c r="F567" s="6">
-        <v>26.7</v>
+        <v>21.74</v>
       </c>
       <c r="G567" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H567" s="5">
-        <v>6331472.9400000004</v>
+        <v>5155289.2</v>
       </c>
       <c r="I567" s="4">
         <v>0</v>
@@ -33780,13 +33771,13 @@
         <v>245</v>
       </c>
       <c r="F568" s="6">
-        <v>25.3</v>
+        <v>4.04</v>
       </c>
       <c r="G568" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H568" s="5">
-        <v>5999485.5899999999</v>
+        <v>958020.62</v>
       </c>
       <c r="I568" s="4">
         <v>0</v>
@@ -33836,13 +33827,13 @@
         <v>245</v>
       </c>
       <c r="F569" s="6">
-        <v>25.7</v>
+        <v>22.12</v>
       </c>
       <c r="G569" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H569" s="5">
-        <v>6094339.1200000001</v>
+        <v>5600488.4400000004</v>
       </c>
       <c r="I569" s="4">
         <v>0</v>
@@ -33892,13 +33883,13 @@
         <v>245</v>
       </c>
       <c r="F570" s="6">
-        <v>21.74</v>
+        <v>2.58</v>
       </c>
       <c r="G570" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H570" s="5">
-        <v>5155289.2</v>
+        <v>653221.53</v>
       </c>
       <c r="I570" s="4">
         <v>0</v>
@@ -33948,13 +33939,13 @@
         <v>245</v>
       </c>
       <c r="F571" s="6">
-        <v>4.04</v>
+        <v>25.2</v>
       </c>
       <c r="G571" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H571" s="5">
-        <v>958020.62</v>
+        <v>6380303.2800000003</v>
       </c>
       <c r="I571" s="4">
         <v>0</v>
@@ -34004,13 +33995,13 @@
         <v>245</v>
       </c>
       <c r="F572" s="6">
-        <v>22.12</v>
+        <v>7.14</v>
       </c>
       <c r="G572" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H572" s="5">
-        <v>5600488.4400000004</v>
+        <v>1807752.6</v>
       </c>
       <c r="I572" s="4">
         <v>0</v>
@@ -34060,13 +34051,13 @@
         <v>245</v>
       </c>
       <c r="F573" s="6">
-        <v>2.58</v>
+        <v>6.76</v>
       </c>
       <c r="G573" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H573" s="5">
-        <v>653221.53</v>
+        <v>1711541.67</v>
       </c>
       <c r="I573" s="4">
         <v>0</v>
@@ -34116,13 +34107,13 @@
         <v>245</v>
       </c>
       <c r="F574" s="6">
-        <v>25.2</v>
+        <v>26.4</v>
       </c>
       <c r="G574" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H574" s="5">
-        <v>6380303.2800000003</v>
+        <v>7507200.8099999996</v>
       </c>
       <c r="I574" s="4">
         <v>0</v>
@@ -34171,14 +34162,14 @@
       <c r="E575" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F575" s="6">
-        <v>7.14</v>
+      <c r="F575" s="4">
+        <v>28</v>
       </c>
       <c r="G575" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H575" s="5">
-        <v>1807752.6</v>
+        <v>7962182.6799999997</v>
       </c>
       <c r="I575" s="4">
         <v>0</v>
@@ -34228,13 +34219,13 @@
         <v>245</v>
       </c>
       <c r="F576" s="6">
-        <v>6.76</v>
+        <v>27.3</v>
       </c>
       <c r="G576" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H576" s="5">
-        <v>1711541.67</v>
+        <v>7763128.1100000003</v>
       </c>
       <c r="I576" s="4">
         <v>0</v>
@@ -34284,13 +34275,13 @@
         <v>245</v>
       </c>
       <c r="F577" s="6">
-        <v>26.4</v>
+        <v>27.12</v>
       </c>
       <c r="G577" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H577" s="5">
-        <v>7507200.8099999996</v>
+        <v>7711942.6500000004</v>
       </c>
       <c r="I577" s="4">
         <v>0</v>
@@ -34339,14 +34330,14 @@
       <c r="E578" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F578" s="4">
-        <v>28</v>
+      <c r="F578" s="6">
+        <v>27.52</v>
       </c>
       <c r="G578" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H578" s="5">
-        <v>7962182.6799999997</v>
+        <v>7825688.1200000001</v>
       </c>
       <c r="I578" s="4">
         <v>0</v>
@@ -34396,13 +34387,13 @@
         <v>245</v>
       </c>
       <c r="F579" s="6">
-        <v>27.3</v>
+        <v>26.74</v>
       </c>
       <c r="G579" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H579" s="5">
-        <v>7763128.1100000003</v>
+        <v>7603884.46</v>
       </c>
       <c r="I579" s="4">
         <v>0</v>
@@ -34452,13 +34443,13 @@
         <v>245</v>
       </c>
       <c r="F580" s="6">
-        <v>27.12</v>
+        <v>26.5</v>
       </c>
       <c r="G580" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H580" s="5">
-        <v>7711942.6500000004</v>
+        <v>7535637.1799999997</v>
       </c>
       <c r="I580" s="4">
         <v>0</v>
@@ -34493,7 +34484,7 @@
     </row>
     <row r="581" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A581" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B581" s="3" t="s">
         <v>0</v>
@@ -34505,16 +34496,16 @@
         <v>2</v>
       </c>
       <c r="E581" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F581" s="6">
-        <v>27.52</v>
+        <v>3</v>
+      </c>
+      <c r="F581" s="4">
+        <v>38</v>
       </c>
       <c r="G581" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H581" s="5">
-        <v>7825688.1200000001</v>
+        <v>14478</v>
       </c>
       <c r="I581" s="4">
         <v>0</v>
@@ -34549,7 +34540,7 @@
     </row>
     <row r="582" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A582" s="3" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B582" s="3" t="s">
         <v>0</v>
@@ -34561,16 +34552,16 @@
         <v>2</v>
       </c>
       <c r="E582" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F582" s="6">
-        <v>26.74</v>
+        <v>3</v>
+      </c>
+      <c r="F582" s="4">
+        <v>7</v>
       </c>
       <c r="G582" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H582" s="5">
-        <v>7603884.46</v>
+        <v>2694.3</v>
       </c>
       <c r="I582" s="4">
         <v>0</v>
@@ -34605,7 +34596,7 @@
     </row>
     <row r="583" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A583" s="3" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="B583" s="3" t="s">
         <v>0</v>
@@ -34617,16 +34608,16 @@
         <v>2</v>
       </c>
       <c r="E583" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F583" s="6">
-        <v>26.5</v>
+        <v>3</v>
+      </c>
+      <c r="F583" s="4">
+        <v>8</v>
       </c>
       <c r="G583" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H583" s="5">
-        <v>7535637.1799999997</v>
+        <v>3079.2</v>
       </c>
       <c r="I583" s="4">
         <v>0</v>
@@ -34661,7 +34652,7 @@
     </row>
     <row r="584" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A584" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B584" s="3" t="s">
         <v>0</v>
@@ -34676,13 +34667,13 @@
         <v>3</v>
       </c>
       <c r="F584" s="4">
-        <v>38</v>
+        <v>3</v>
       </c>
       <c r="G584" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H584" s="5">
-        <v>14478</v>
+        <v>41996.4</v>
       </c>
       <c r="I584" s="4">
         <v>0</v>
@@ -34717,7 +34708,7 @@
     </row>
     <row r="585" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A585" s="3" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B585" s="3" t="s">
         <v>0</v>
@@ -34732,13 +34723,13 @@
         <v>3</v>
       </c>
       <c r="F585" s="4">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G585" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H585" s="5">
-        <v>2694.3</v>
+        <v>42314.02</v>
       </c>
       <c r="I585" s="4">
         <v>0</v>
@@ -34773,7 +34764,7 @@
     </row>
     <row r="586" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A586" s="3" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="B586" s="3" t="s">
         <v>0</v>
@@ -34788,13 +34779,13 @@
         <v>3</v>
       </c>
       <c r="F586" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G586" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H586" s="5">
-        <v>3079.2</v>
+        <v>4050.54</v>
       </c>
       <c r="I586" s="4">
         <v>0</v>
@@ -34829,7 +34820,7 @@
     </row>
     <row r="587" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A587" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B587" s="3" t="s">
         <v>0</v>
@@ -34844,13 +34835,13 @@
         <v>3</v>
       </c>
       <c r="F587" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G587" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H587" s="5">
-        <v>41996.4</v>
+        <v>2025.27</v>
       </c>
       <c r="I587" s="4">
         <v>0</v>
@@ -34885,7 +34876,7 @@
     </row>
     <row r="588" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A588" s="3" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B588" s="3" t="s">
         <v>0</v>
@@ -34900,13 +34891,13 @@
         <v>3</v>
       </c>
       <c r="F588" s="4">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G588" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H588" s="5">
-        <v>42314.02</v>
+        <v>3420</v>
       </c>
       <c r="I588" s="4">
         <v>0</v>
@@ -34941,7 +34932,7 @@
     </row>
     <row r="589" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A589" s="3" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B589" s="3" t="s">
         <v>0</v>
@@ -34956,13 +34947,13 @@
         <v>3</v>
       </c>
       <c r="F589" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G589" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H589" s="5">
-        <v>4050.54</v>
+        <v>4598</v>
       </c>
       <c r="I589" s="4">
         <v>0</v>
@@ -34997,7 +34988,7 @@
     </row>
     <row r="590" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A590" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B590" s="3" t="s">
         <v>0</v>
@@ -35012,13 +35003,13 @@
         <v>3</v>
       </c>
       <c r="F590" s="4">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G590" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H590" s="5">
-        <v>2025.27</v>
+        <v>5517.6</v>
       </c>
       <c r="I590" s="4">
         <v>0</v>
@@ -35053,7 +35044,7 @@
     </row>
     <row r="591" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A591" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="B591" s="3" t="s">
         <v>0</v>
@@ -35068,13 +35059,13 @@
         <v>3</v>
       </c>
       <c r="F591" s="4">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="G591" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H591" s="5">
-        <v>3420</v>
+        <v>6119.15</v>
       </c>
       <c r="I591" s="4">
         <v>0</v>
@@ -35109,7 +35100,7 @@
     </row>
     <row r="592" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A592" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="B592" s="3" t="s">
         <v>0</v>
@@ -35124,13 +35115,13 @@
         <v>3</v>
       </c>
       <c r="F592" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G592" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H592" s="5">
-        <v>4598</v>
+        <v>999.85</v>
       </c>
       <c r="I592" s="4">
         <v>0</v>
@@ -35165,7 +35156,7 @@
     </row>
     <row r="593" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A593" s="3" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B593" s="3" t="s">
         <v>0</v>
@@ -35180,13 +35171,13 @@
         <v>3</v>
       </c>
       <c r="F593" s="4">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G593" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H593" s="5">
-        <v>5517.6</v>
+        <v>22251.75</v>
       </c>
       <c r="I593" s="4">
         <v>0</v>
@@ -35221,7 +35212,7 @@
     </row>
     <row r="594" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A594" s="3" t="s">
-        <v>277</v>
+        <v>354</v>
       </c>
       <c r="B594" s="3" t="s">
         <v>0</v>
@@ -35236,13 +35227,13 @@
         <v>3</v>
       </c>
       <c r="F594" s="4">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G594" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H594" s="5">
-        <v>6119.15</v>
+        <v>62746.48</v>
       </c>
       <c r="I594" s="4">
         <v>0</v>
@@ -35277,7 +35268,7 @@
     </row>
     <row r="595" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A595" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B595" s="3" t="s">
         <v>0</v>
@@ -35292,13 +35283,13 @@
         <v>3</v>
       </c>
       <c r="F595" s="4">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="G595" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H595" s="5">
-        <v>999.85</v>
+        <v>11017.1</v>
       </c>
       <c r="I595" s="4">
         <v>0</v>
@@ -35333,7 +35324,7 @@
     </row>
     <row r="596" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A596" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B596" s="3" t="s">
         <v>0</v>
@@ -35348,13 +35339,13 @@
         <v>3</v>
       </c>
       <c r="F596" s="4">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="G596" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H596" s="5">
-        <v>22251.75</v>
+        <v>12529.77</v>
       </c>
       <c r="I596" s="4">
         <v>0</v>
@@ -35389,7 +35380,7 @@
     </row>
     <row r="597" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A597" s="3" t="s">
-        <v>354</v>
+        <v>282</v>
       </c>
       <c r="B597" s="3" t="s">
         <v>0</v>
@@ -35404,13 +35395,13 @@
         <v>3</v>
       </c>
       <c r="F597" s="4">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G597" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H597" s="5">
-        <v>62746.48</v>
+        <v>4178.8999999999996</v>
       </c>
       <c r="I597" s="4">
         <v>0</v>
@@ -35445,7 +35436,7 @@
     </row>
     <row r="598" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A598" s="3" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B598" s="3" t="s">
         <v>0</v>
@@ -35460,13 +35451,13 @@
         <v>3</v>
       </c>
       <c r="F598" s="4">
-        <v>29</v>
+        <v>6</v>
       </c>
       <c r="G598" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H598" s="5">
-        <v>11017.1</v>
+        <v>72221.83</v>
       </c>
       <c r="I598" s="4">
         <v>0</v>
@@ -35501,7 +35492,7 @@
     </row>
     <row r="599" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A599" s="3" t="s">
-        <v>281</v>
+        <v>455</v>
       </c>
       <c r="B599" s="3" t="s">
         <v>0</v>
@@ -35516,13 +35507,13 @@
         <v>3</v>
       </c>
       <c r="F599" s="4">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G599" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H599" s="5">
-        <v>12529.77</v>
+        <v>44996.4</v>
       </c>
       <c r="I599" s="4">
         <v>0</v>
@@ -35557,7 +35548,7 @@
     </row>
     <row r="600" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A600" s="3" t="s">
-        <v>282</v>
+        <v>461</v>
       </c>
       <c r="B600" s="3" t="s">
         <v>0</v>
@@ -35572,13 +35563,13 @@
         <v>3</v>
       </c>
       <c r="F600" s="4">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G600" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H600" s="5">
-        <v>4178.8999999999996</v>
+        <v>29930.93</v>
       </c>
       <c r="I600" s="4">
         <v>0</v>
@@ -35613,7 +35604,7 @@
     </row>
     <row r="601" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A601" s="3" t="s">
-        <v>283</v>
+        <v>461</v>
       </c>
       <c r="B601" s="3" t="s">
         <v>0</v>
@@ -35628,13 +35619,13 @@
         <v>3</v>
       </c>
       <c r="F601" s="4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G601" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H601" s="5">
-        <v>72221.83</v>
+        <v>59861.87</v>
       </c>
       <c r="I601" s="4">
         <v>0</v>
@@ -35669,7 +35660,7 @@
     </row>
     <row r="602" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A602" s="3" t="s">
-        <v>455</v>
+        <v>284</v>
       </c>
       <c r="B602" s="3" t="s">
         <v>0</v>
@@ -35684,13 +35675,13 @@
         <v>3</v>
       </c>
       <c r="F602" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G602" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H602" s="5">
-        <v>44996.4</v>
+        <v>11755.02</v>
       </c>
       <c r="I602" s="4">
         <v>0</v>
@@ -35725,7 +35716,7 @@
     </row>
     <row r="603" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A603" s="3" t="s">
-        <v>461</v>
+        <v>285</v>
       </c>
       <c r="B603" s="3" t="s">
         <v>0</v>
@@ -35740,13 +35731,13 @@
         <v>3</v>
       </c>
       <c r="F603" s="4">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G603" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H603" s="5">
-        <v>29930.93</v>
+        <v>37077.949999999997</v>
       </c>
       <c r="I603" s="4">
         <v>0</v>
@@ -35781,7 +35772,7 @@
     </row>
     <row r="604" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A604" s="3" t="s">
-        <v>461</v>
+        <v>286</v>
       </c>
       <c r="B604" s="3" t="s">
         <v>0</v>
@@ -35796,13 +35787,13 @@
         <v>3</v>
       </c>
       <c r="F604" s="4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="G604" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H604" s="5">
-        <v>59861.87</v>
+        <v>3039.2</v>
       </c>
       <c r="I604" s="4">
         <v>0</v>
@@ -35837,7 +35828,7 @@
     </row>
     <row r="605" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A605" s="3" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="B605" s="3" t="s">
         <v>0</v>
@@ -35852,13 +35843,13 @@
         <v>3</v>
       </c>
       <c r="F605" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G605" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H605" s="5">
-        <v>11755.02</v>
+        <v>759.8</v>
       </c>
       <c r="I605" s="4">
         <v>0</v>
@@ -35893,7 +35884,7 @@
     </row>
     <row r="606" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A606" s="3" t="s">
-        <v>285</v>
+        <v>488</v>
       </c>
       <c r="B606" s="3" t="s">
         <v>0</v>
@@ -35914,7 +35905,7 @@
         <v>4</v>
       </c>
       <c r="H606" s="5">
-        <v>37077.949999999997</v>
+        <v>0</v>
       </c>
       <c r="I606" s="4">
         <v>0</v>
@@ -35949,7 +35940,7 @@
     </row>
     <row r="607" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A607" s="3" t="s">
-        <v>286</v>
+        <v>483</v>
       </c>
       <c r="B607" s="3" t="s">
         <v>0</v>
@@ -35964,13 +35955,13 @@
         <v>3</v>
       </c>
       <c r="F607" s="4">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G607" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H607" s="5">
-        <v>3039.2</v>
+        <v>372565.75</v>
       </c>
       <c r="I607" s="4">
         <v>0</v>
@@ -36005,7 +35996,7 @@
     </row>
     <row r="608" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A608" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B608" s="3" t="s">
         <v>0</v>
@@ -36020,13 +36011,13 @@
         <v>3</v>
       </c>
       <c r="F608" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G608" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H608" s="5">
-        <v>759.8</v>
+        <v>18933.62</v>
       </c>
       <c r="I608" s="4">
         <v>0</v>
@@ -36061,7 +36052,7 @@
     </row>
     <row r="609" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A609" s="3" t="s">
-        <v>491</v>
+        <v>446</v>
       </c>
       <c r="B609" s="3" t="s">
         <v>0</v>
@@ -36076,13 +36067,13 @@
         <v>3</v>
       </c>
       <c r="F609" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G609" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H609" s="5">
-        <v>0</v>
+        <v>18448.599999999999</v>
       </c>
       <c r="I609" s="4">
         <v>0</v>
@@ -36117,7 +36108,7 @@
     </row>
     <row r="610" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A610" s="3" t="s">
-        <v>486</v>
+        <v>447</v>
       </c>
       <c r="B610" s="3" t="s">
         <v>0</v>
@@ -36138,7 +36129,7 @@
         <v>4</v>
       </c>
       <c r="H610" s="5">
-        <v>372565.75</v>
+        <v>30138.51</v>
       </c>
       <c r="I610" s="4">
         <v>0</v>
@@ -36173,7 +36164,7 @@
     </row>
     <row r="611" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A611" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B611" s="3" t="s">
         <v>0</v>
@@ -36188,13 +36179,13 @@
         <v>3</v>
       </c>
       <c r="F611" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G611" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H611" s="5">
-        <v>18933.62</v>
+        <v>105341.16</v>
       </c>
       <c r="I611" s="4">
         <v>0</v>
@@ -36229,7 +36220,7 @@
     </row>
     <row r="612" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A612" s="3" t="s">
-        <v>446</v>
+        <v>454</v>
       </c>
       <c r="B612" s="3" t="s">
         <v>0</v>
@@ -36244,13 +36235,13 @@
         <v>3</v>
       </c>
       <c r="F612" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G612" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H612" s="5">
-        <v>18448.599999999999</v>
+        <v>27051.85</v>
       </c>
       <c r="I612" s="4">
         <v>0</v>
@@ -36285,7 +36276,7 @@
     </row>
     <row r="613" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A613" s="3" t="s">
-        <v>447</v>
+        <v>454</v>
       </c>
       <c r="B613" s="3" t="s">
         <v>0</v>
@@ -36300,13 +36291,13 @@
         <v>3</v>
       </c>
       <c r="F613" s="4">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="G613" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H613" s="5">
-        <v>30138.51</v>
+        <v>94681.48</v>
       </c>
       <c r="I613" s="4">
         <v>0</v>
@@ -36341,7 +36332,7 @@
     </row>
     <row r="614" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A614" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B614" s="3" t="s">
         <v>0</v>
@@ -36350,19 +36341,19 @@
         <v>1</v>
       </c>
       <c r="D614" s="3" t="s">
-        <v>2</v>
+        <v>261</v>
       </c>
       <c r="E614" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F614" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G614" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H614" s="5">
-        <v>81475.240000000005</v>
+        <v>0</v>
       </c>
       <c r="I614" s="4">
         <v>0</v>
@@ -36397,7 +36388,7 @@
     </row>
     <row r="615" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A615" s="3" t="s">
-        <v>454</v>
+        <v>291</v>
       </c>
       <c r="B615" s="3" t="s">
         <v>0</v>
@@ -36409,16 +36400,16 @@
         <v>2</v>
       </c>
       <c r="E615" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F615" s="4">
-        <v>2</v>
+        <v>245</v>
+      </c>
+      <c r="F615" s="6">
+        <v>10.82</v>
       </c>
       <c r="G615" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H615" s="5">
-        <v>27051.85</v>
+        <v>4673347.3499999996</v>
       </c>
       <c r="I615" s="4">
         <v>0</v>
@@ -36453,7 +36444,7 @@
     </row>
     <row r="616" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A616" s="3" t="s">
-        <v>454</v>
+        <v>292</v>
       </c>
       <c r="B616" s="3" t="s">
         <v>0</v>
@@ -36468,13 +36459,13 @@
         <v>3</v>
       </c>
       <c r="F616" s="4">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G616" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H616" s="5">
-        <v>94681.48</v>
+        <v>0</v>
       </c>
       <c r="I616" s="4">
         <v>0</v>
@@ -36509,7 +36500,7 @@
     </row>
     <row r="617" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A617" s="3" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B617" s="3" t="s">
         <v>0</v>
@@ -36518,13 +36509,13 @@
         <v>1</v>
       </c>
       <c r="D617" s="3" t="s">
-        <v>261</v>
+        <v>2</v>
       </c>
       <c r="E617" s="3" t="s">
         <v>3</v>
       </c>
       <c r="F617" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G617" s="3" t="s">
         <v>4</v>
@@ -36565,7 +36556,7 @@
     </row>
     <row r="618" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A618" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="B618" s="3" t="s">
         <v>0</v>
@@ -36577,16 +36568,16 @@
         <v>2</v>
       </c>
       <c r="E618" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="F618" s="6">
-        <v>10.82</v>
+        <v>3</v>
+      </c>
+      <c r="F618" s="4">
+        <v>5</v>
       </c>
       <c r="G618" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H618" s="5">
-        <v>4673347.3499999996</v>
+        <v>0</v>
       </c>
       <c r="I618" s="4">
         <v>0</v>
@@ -36621,7 +36612,7 @@
     </row>
     <row r="619" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A619" s="3" t="s">
-        <v>292</v>
+        <v>448</v>
       </c>
       <c r="B619" s="3" t="s">
         <v>0</v>
@@ -36636,7 +36627,7 @@
         <v>3</v>
       </c>
       <c r="F619" s="4">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G619" s="3" t="s">
         <v>4</v>
@@ -36677,7 +36668,7 @@
     </row>
     <row r="620" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A620" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B620" s="3" t="s">
         <v>0</v>
@@ -36692,7 +36683,7 @@
         <v>3</v>
       </c>
       <c r="F620" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G620" s="3" t="s">
         <v>4</v>
@@ -36733,7 +36724,7 @@
     </row>
     <row r="621" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A621" s="3" t="s">
-        <v>294</v>
+        <v>394</v>
       </c>
       <c r="B621" s="3" t="s">
         <v>0</v>
@@ -36748,7 +36739,7 @@
         <v>3</v>
       </c>
       <c r="F621" s="4">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G621" s="3" t="s">
         <v>4</v>
@@ -36789,7 +36780,7 @@
     </row>
     <row r="622" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A622" s="3" t="s">
-        <v>448</v>
+        <v>296</v>
       </c>
       <c r="B622" s="3" t="s">
         <v>0</v>
@@ -36804,7 +36795,7 @@
         <v>3</v>
       </c>
       <c r="F622" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G622" s="3" t="s">
         <v>4</v>
@@ -36845,7 +36836,7 @@
     </row>
     <row r="623" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A623" s="3" t="s">
-        <v>295</v>
+        <v>349</v>
       </c>
       <c r="B623" s="3" t="s">
         <v>0</v>
@@ -36860,7 +36851,7 @@
         <v>3</v>
       </c>
       <c r="F623" s="4">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G623" s="3" t="s">
         <v>4</v>
@@ -36901,7 +36892,7 @@
     </row>
     <row r="624" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A624" s="3" t="s">
-        <v>394</v>
+        <v>297</v>
       </c>
       <c r="B624" s="3" t="s">
         <v>0</v>
@@ -36957,7 +36948,7 @@
     </row>
     <row r="625" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A625" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B625" s="3" t="s">
         <v>0</v>
@@ -36972,7 +36963,7 @@
         <v>3</v>
       </c>
       <c r="F625" s="4">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G625" s="3" t="s">
         <v>4</v>
@@ -37013,7 +37004,7 @@
     </row>
     <row r="626" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A626" s="3" t="s">
-        <v>349</v>
+        <v>299</v>
       </c>
       <c r="B626" s="3" t="s">
         <v>0</v>
@@ -37028,7 +37019,7 @@
         <v>3</v>
       </c>
       <c r="F626" s="4">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="G626" s="3" t="s">
         <v>4</v>
@@ -37069,7 +37060,7 @@
     </row>
     <row r="627" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A627" s="3" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="B627" s="3" t="s">
         <v>0</v>
@@ -37084,7 +37075,7 @@
         <v>3</v>
       </c>
       <c r="F627" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G627" s="3" t="s">
         <v>4</v>
@@ -37125,7 +37116,7 @@
     </row>
     <row r="628" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A628" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="B628" s="3" t="s">
         <v>0</v>
@@ -37140,7 +37131,7 @@
         <v>3</v>
       </c>
       <c r="F628" s="4">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="G628" s="3" t="s">
         <v>4</v>
@@ -37181,7 +37172,7 @@
     </row>
     <row r="629" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A629" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B629" s="3" t="s">
         <v>0</v>
@@ -37196,7 +37187,7 @@
         <v>3</v>
       </c>
       <c r="F629" s="4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G629" s="3" t="s">
         <v>4</v>
@@ -37237,7 +37228,7 @@
     </row>
     <row r="630" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A630" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B630" s="3" t="s">
         <v>0</v>
@@ -37252,7 +37243,7 @@
         <v>3</v>
       </c>
       <c r="F630" s="4">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G630" s="3" t="s">
         <v>4</v>
@@ -37293,7 +37284,7 @@
     </row>
     <row r="631" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A631" s="3" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B631" s="3" t="s">
         <v>0</v>
@@ -37349,7 +37340,7 @@
     </row>
     <row r="632" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A632" s="3" t="s">
-        <v>302</v>
+        <v>350</v>
       </c>
       <c r="B632" s="3" t="s">
         <v>0</v>
@@ -37364,7 +37355,7 @@
         <v>3</v>
       </c>
       <c r="F632" s="4">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G632" s="3" t="s">
         <v>4</v>
@@ -37405,7 +37396,7 @@
     </row>
     <row r="633" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A633" s="3" t="s">
-        <v>303</v>
+        <v>351</v>
       </c>
       <c r="B633" s="3" t="s">
         <v>0</v>
@@ -37420,7 +37411,7 @@
         <v>3</v>
       </c>
       <c r="F633" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G633" s="3" t="s">
         <v>4</v>
@@ -37461,7 +37452,7 @@
     </row>
     <row r="634" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A634" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B634" s="3" t="s">
         <v>0</v>
@@ -37476,7 +37467,7 @@
         <v>3</v>
       </c>
       <c r="F634" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G634" s="3" t="s">
         <v>4</v>
@@ -37517,7 +37508,7 @@
     </row>
     <row r="635" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A635" s="3" t="s">
-        <v>350</v>
+        <v>306</v>
       </c>
       <c r="B635" s="3" t="s">
         <v>0</v>
@@ -37573,7 +37564,7 @@
     </row>
     <row r="636" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A636" s="3" t="s">
-        <v>351</v>
+        <v>307</v>
       </c>
       <c r="B636" s="3" t="s">
         <v>0</v>
@@ -37588,7 +37579,7 @@
         <v>3</v>
       </c>
       <c r="F636" s="4">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="G636" s="3" t="s">
         <v>4</v>
@@ -37629,7 +37620,7 @@
     </row>
     <row r="637" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A637" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B637" s="3" t="s">
         <v>0</v>
@@ -37644,7 +37635,7 @@
         <v>3</v>
       </c>
       <c r="F637" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G637" s="3" t="s">
         <v>4</v>
@@ -37685,7 +37676,7 @@
     </row>
     <row r="638" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A638" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B638" s="3" t="s">
         <v>0</v>
@@ -37700,7 +37691,7 @@
         <v>3</v>
       </c>
       <c r="F638" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G638" s="3" t="s">
         <v>4</v>
@@ -37741,7 +37732,7 @@
     </row>
     <row r="639" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A639" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B639" s="3" t="s">
         <v>0</v>
@@ -37756,7 +37747,7 @@
         <v>3</v>
       </c>
       <c r="F639" s="4">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="G639" s="3" t="s">
         <v>4</v>
@@ -37797,7 +37788,7 @@
     </row>
     <row r="640" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A640" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B640" s="3" t="s">
         <v>0</v>
@@ -37812,7 +37803,7 @@
         <v>3</v>
       </c>
       <c r="F640" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G640" s="3" t="s">
         <v>4</v>
@@ -37853,7 +37844,7 @@
     </row>
     <row r="641" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A641" s="3" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B641" s="3" t="s">
         <v>0</v>
@@ -37868,7 +37859,7 @@
         <v>3</v>
       </c>
       <c r="F641" s="4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G641" s="3" t="s">
         <v>4</v>
@@ -37909,7 +37900,7 @@
     </row>
     <row r="642" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A642" s="3" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B642" s="3" t="s">
         <v>0</v>
@@ -37924,7 +37915,7 @@
         <v>3</v>
       </c>
       <c r="F642" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G642" s="3" t="s">
         <v>4</v>
@@ -37965,7 +37956,7 @@
     </row>
     <row r="643" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A643" s="3" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B643" s="3" t="s">
         <v>0</v>
@@ -37980,7 +37971,7 @@
         <v>3</v>
       </c>
       <c r="F643" s="4">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G643" s="3" t="s">
         <v>4</v>
@@ -38021,7 +38012,7 @@
     </row>
     <row r="644" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A644" s="3" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B644" s="3" t="s">
         <v>0</v>
@@ -38036,7 +38027,7 @@
         <v>3</v>
       </c>
       <c r="F644" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G644" s="3" t="s">
         <v>4</v>
@@ -38077,7 +38068,7 @@
     </row>
     <row r="645" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A645" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B645" s="3" t="s">
         <v>0</v>
@@ -38133,7 +38124,7 @@
     </row>
     <row r="646" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A646" s="3" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="B646" s="3" t="s">
         <v>0</v>
@@ -38148,7 +38139,7 @@
         <v>3</v>
       </c>
       <c r="F646" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G646" s="3" t="s">
         <v>4</v>
@@ -38189,7 +38180,7 @@
     </row>
     <row r="647" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A647" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B647" s="3" t="s">
         <v>0</v>
@@ -38204,7 +38195,7 @@
         <v>3</v>
       </c>
       <c r="F647" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G647" s="3" t="s">
         <v>4</v>
@@ -38245,7 +38236,7 @@
     </row>
     <row r="648" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A648" s="3" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B648" s="3" t="s">
         <v>0</v>
@@ -38260,7 +38251,7 @@
         <v>3</v>
       </c>
       <c r="F648" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G648" s="3" t="s">
         <v>4</v>
@@ -38301,7 +38292,7 @@
     </row>
     <row r="649" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A649" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B649" s="3" t="s">
         <v>0</v>
@@ -38316,7 +38307,7 @@
         <v>3</v>
       </c>
       <c r="F649" s="4">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G649" s="3" t="s">
         <v>4</v>
@@ -38357,7 +38348,7 @@
     </row>
     <row r="650" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A650" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="B650" s="3" t="s">
         <v>0</v>
@@ -38413,7 +38404,7 @@
     </row>
     <row r="651" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A651" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B651" s="3" t="s">
         <v>0</v>
@@ -38427,14 +38418,14 @@
       <c r="E651" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F651" s="4">
-        <v>6</v>
+      <c r="F651" s="6">
+        <v>0.63400000000000001</v>
       </c>
       <c r="G651" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H651" s="5">
-        <v>0</v>
+        <v>870576.49</v>
       </c>
       <c r="I651" s="4">
         <v>0</v>
@@ -38469,7 +38460,7 @@
     </row>
     <row r="652" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A652" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B652" s="3" t="s">
         <v>0</v>
@@ -38484,13 +38475,13 @@
         <v>3</v>
       </c>
       <c r="F652" s="4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="G652" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H652" s="5">
-        <v>0</v>
+        <v>1373149.03</v>
       </c>
       <c r="I652" s="4">
         <v>0</v>
@@ -38525,7 +38516,7 @@
     </row>
     <row r="653" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A653" s="3" t="s">
-        <v>321</v>
+        <v>484</v>
       </c>
       <c r="B653" s="3" t="s">
         <v>0</v>
@@ -38546,7 +38537,7 @@
         <v>4</v>
       </c>
       <c r="H653" s="5">
-        <v>0</v>
+        <v>128155.5</v>
       </c>
       <c r="I653" s="4">
         <v>0</v>
@@ -38581,7 +38572,7 @@
     </row>
     <row r="654" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A654" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B654" s="3" t="s">
         <v>0</v>
@@ -38595,14 +38586,14 @@
       <c r="E654" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F654" s="6">
-        <v>0.63400000000000001</v>
+      <c r="F654" s="4">
+        <v>2</v>
       </c>
       <c r="G654" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H654" s="5">
-        <v>870576.49</v>
+        <v>4905908.92</v>
       </c>
       <c r="I654" s="4">
         <v>0</v>
@@ -38637,7 +38628,7 @@
     </row>
     <row r="655" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A655" s="3" t="s">
-        <v>322</v>
+        <v>396</v>
       </c>
       <c r="B655" s="3" t="s">
         <v>0</v>
@@ -38652,19 +38643,19 @@
         <v>3</v>
       </c>
       <c r="F655" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G655" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H655" s="5">
-        <v>1373149.03</v>
+        <v>0</v>
       </c>
       <c r="I655" s="4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J655" s="5">
-        <v>0</v>
+        <v>25504446.600000001</v>
       </c>
       <c r="K655" s="4">
         <v>0</v>
@@ -38693,7 +38684,7 @@
     </row>
     <row r="656" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A656" s="3" t="s">
-        <v>487</v>
+        <v>356</v>
       </c>
       <c r="B656" s="3" t="s">
         <v>0</v>
@@ -38714,7 +38705,7 @@
         <v>4</v>
       </c>
       <c r="H656" s="5">
-        <v>128155.5</v>
+        <v>16843.099999999999</v>
       </c>
       <c r="I656" s="4">
         <v>0</v>
@@ -38749,7 +38740,7 @@
     </row>
     <row r="657" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A657" s="3" t="s">
-        <v>323</v>
+        <v>397</v>
       </c>
       <c r="B657" s="3" t="s">
         <v>0</v>
@@ -38764,19 +38755,19 @@
         <v>3</v>
       </c>
       <c r="F657" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G657" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H657" s="5">
-        <v>4905908.92</v>
+        <v>0</v>
       </c>
       <c r="I657" s="4">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="J657" s="5">
-        <v>0</v>
+        <v>3009052.8</v>
       </c>
       <c r="K657" s="4">
         <v>0</v>
@@ -38805,7 +38796,7 @@
     </row>
     <row r="658" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A658" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B658" s="3" t="s">
         <v>0</v>
@@ -38829,10 +38820,10 @@
         <v>0</v>
       </c>
       <c r="I658" s="4">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J658" s="5">
-        <v>25504446.600000001</v>
+        <v>5464906.2000000002</v>
       </c>
       <c r="K658" s="4">
         <v>0</v>
@@ -38861,7 +38852,7 @@
     </row>
     <row r="659" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A659" s="3" t="s">
-        <v>356</v>
+        <v>399</v>
       </c>
       <c r="B659" s="3" t="s">
         <v>0</v>
@@ -38876,19 +38867,19 @@
         <v>3</v>
       </c>
       <c r="F659" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G659" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H659" s="5">
-        <v>16843.099999999999</v>
+        <v>0</v>
       </c>
       <c r="I659" s="4">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J659" s="5">
-        <v>0</v>
+        <v>7097573.4000000004</v>
       </c>
       <c r="K659" s="4">
         <v>0</v>
@@ -38917,7 +38908,7 @@
     </row>
     <row r="660" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A660" s="3" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B660" s="3" t="s">
         <v>0</v>
@@ -38941,10 +38932,10 @@
         <v>0</v>
       </c>
       <c r="I660" s="4">
-        <v>312</v>
+        <v>2</v>
       </c>
       <c r="J660" s="5">
-        <v>3009052.8</v>
+        <v>8088126.5999999996</v>
       </c>
       <c r="K660" s="4">
         <v>0</v>
@@ -38973,7 +38964,7 @@
     </row>
     <row r="661" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A661" s="3" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B661" s="3" t="s">
         <v>0</v>
@@ -38997,10 +38988,10 @@
         <v>0</v>
       </c>
       <c r="I661" s="4">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J661" s="5">
-        <v>5464906.2000000002</v>
+        <v>1922958</v>
       </c>
       <c r="K661" s="4">
         <v>0</v>
@@ -39029,7 +39020,7 @@
     </row>
     <row r="662" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A662" s="3" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="B662" s="3" t="s">
         <v>0</v>
@@ -39053,10 +39044,10 @@
         <v>0</v>
       </c>
       <c r="I662" s="4">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="J662" s="5">
-        <v>7097573.4000000004</v>
+        <v>293195.40000000002</v>
       </c>
       <c r="K662" s="4">
         <v>0</v>
@@ -39085,7 +39076,7 @@
     </row>
     <row r="663" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A663" s="3" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="B663" s="3" t="s">
         <v>0</v>
@@ -39109,10 +39100,10 @@
         <v>0</v>
       </c>
       <c r="I663" s="4">
-        <v>2</v>
+        <v>78</v>
       </c>
       <c r="J663" s="5">
-        <v>8088126.5999999996</v>
+        <v>1142725.92</v>
       </c>
       <c r="K663" s="4">
         <v>0</v>
@@ -39141,7 +39132,7 @@
     </row>
     <row r="664" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A664" s="3" t="s">
-        <v>401</v>
+        <v>324</v>
       </c>
       <c r="B664" s="3" t="s">
         <v>0</v>
@@ -39156,19 +39147,19 @@
         <v>3</v>
       </c>
       <c r="F664" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G664" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H664" s="5">
-        <v>0</v>
+        <v>504187.33</v>
       </c>
       <c r="I664" s="4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J664" s="5">
-        <v>1922958</v>
+        <v>0</v>
       </c>
       <c r="K664" s="4">
         <v>0</v>
@@ -39197,7 +39188,7 @@
     </row>
     <row r="665" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A665" s="3" t="s">
-        <v>402</v>
+        <v>325</v>
       </c>
       <c r="B665" s="3" t="s">
         <v>0</v>
@@ -39212,19 +39203,19 @@
         <v>3</v>
       </c>
       <c r="F665" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G665" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H665" s="5">
-        <v>0</v>
+        <v>310702.5</v>
       </c>
       <c r="I665" s="4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J665" s="5">
-        <v>293195.40000000002</v>
+        <v>0</v>
       </c>
       <c r="K665" s="4">
         <v>0</v>
@@ -39253,7 +39244,7 @@
     </row>
     <row r="666" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A666" s="3" t="s">
-        <v>403</v>
+        <v>352</v>
       </c>
       <c r="B666" s="3" t="s">
         <v>0</v>
@@ -39268,7 +39259,7 @@
         <v>3</v>
       </c>
       <c r="F666" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G666" s="3" t="s">
         <v>4</v>
@@ -39277,10 +39268,10 @@
         <v>0</v>
       </c>
       <c r="I666" s="4">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="J666" s="5">
-        <v>1142725.92</v>
+        <v>0</v>
       </c>
       <c r="K666" s="4">
         <v>0</v>
@@ -39309,7 +39300,7 @@
     </row>
     <row r="667" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A667" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B667" s="3" t="s">
         <v>0</v>
@@ -39330,7 +39321,7 @@
         <v>4</v>
       </c>
       <c r="H667" s="5">
-        <v>504187.33</v>
+        <v>0</v>
       </c>
       <c r="I667" s="4">
         <v>0</v>
@@ -39365,7 +39356,7 @@
     </row>
     <row r="668" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A668" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B668" s="3" t="s">
         <v>0</v>
@@ -39380,13 +39371,13 @@
         <v>3</v>
       </c>
       <c r="F668" s="4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G668" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H668" s="5">
-        <v>310702.5</v>
+        <v>0</v>
       </c>
       <c r="I668" s="4">
         <v>0</v>
@@ -39421,7 +39412,7 @@
     </row>
     <row r="669" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A669" s="3" t="s">
-        <v>352</v>
+        <v>328</v>
       </c>
       <c r="B669" s="3" t="s">
         <v>0</v>
@@ -39477,7 +39468,7 @@
     </row>
     <row r="670" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A670" s="3" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B670" s="3" t="s">
         <v>0</v>
@@ -39492,7 +39483,7 @@
         <v>3</v>
       </c>
       <c r="F670" s="4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G670" s="3" t="s">
         <v>4</v>
@@ -39533,7 +39524,7 @@
     </row>
     <row r="671" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A671" s="3" t="s">
-        <v>327</v>
+        <v>404</v>
       </c>
       <c r="B671" s="3" t="s">
         <v>0</v>
@@ -39548,7 +39539,7 @@
         <v>3</v>
       </c>
       <c r="F671" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G671" s="3" t="s">
         <v>4</v>
@@ -39557,10 +39548,10 @@
         <v>0</v>
       </c>
       <c r="I671" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J671" s="5">
-        <v>0</v>
+        <v>2121034.7999999998</v>
       </c>
       <c r="K671" s="4">
         <v>0</v>
@@ -39589,7 +39580,7 @@
     </row>
     <row r="672" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A672" s="3" t="s">
-        <v>328</v>
+        <v>405</v>
       </c>
       <c r="B672" s="3" t="s">
         <v>0</v>
@@ -39604,7 +39595,7 @@
         <v>3</v>
       </c>
       <c r="F672" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G672" s="3" t="s">
         <v>4</v>
@@ -39613,10 +39604,10 @@
         <v>0</v>
       </c>
       <c r="I672" s="4">
-        <v>0</v>
+        <v>312</v>
       </c>
       <c r="J672" s="5">
-        <v>0</v>
+        <v>369532.8</v>
       </c>
       <c r="K672" s="4">
         <v>0</v>
@@ -39645,7 +39636,7 @@
     </row>
     <row r="673" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A673" s="3" t="s">
-        <v>329</v>
+        <v>449</v>
       </c>
       <c r="B673" s="3" t="s">
         <v>0</v>
@@ -39660,7 +39651,7 @@
         <v>3</v>
       </c>
       <c r="F673" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G673" s="3" t="s">
         <v>4</v>
@@ -39701,7 +39692,7 @@
     </row>
     <row r="674" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A674" s="3" t="s">
-        <v>404</v>
+        <v>353</v>
       </c>
       <c r="B674" s="3" t="s">
         <v>0</v>
@@ -39716,7 +39707,7 @@
         <v>3</v>
       </c>
       <c r="F674" s="4">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G674" s="3" t="s">
         <v>4</v>
@@ -39725,10 +39716,10 @@
         <v>0</v>
       </c>
       <c r="I674" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J674" s="5">
-        <v>2121034.7999999998</v>
+        <v>0</v>
       </c>
       <c r="K674" s="4">
         <v>0</v>
@@ -39757,7 +39748,7 @@
     </row>
     <row r="675" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A675" s="3" t="s">
-        <v>405</v>
+        <v>489</v>
       </c>
       <c r="B675" s="3" t="s">
         <v>0</v>
@@ -39772,19 +39763,19 @@
         <v>3</v>
       </c>
       <c r="F675" s="4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G675" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H675" s="5">
-        <v>0</v>
+        <v>68462.52</v>
       </c>
       <c r="I675" s="4">
-        <v>312</v>
+        <v>0</v>
       </c>
       <c r="J675" s="5">
-        <v>369532.8</v>
+        <v>0</v>
       </c>
       <c r="K675" s="4">
         <v>0</v>
@@ -39813,7 +39804,7 @@
     </row>
     <row r="676" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A676" s="3" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B676" s="3" t="s">
         <v>0</v>
@@ -39869,7 +39860,7 @@
     </row>
     <row r="677" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A677" s="3" t="s">
-        <v>353</v>
+        <v>451</v>
       </c>
       <c r="B677" s="3" t="s">
         <v>0</v>
@@ -39884,7 +39875,7 @@
         <v>3</v>
       </c>
       <c r="F677" s="4">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G677" s="3" t="s">
         <v>4</v>
@@ -39925,7 +39916,7 @@
     </row>
     <row r="678" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A678" s="3" t="s">
-        <v>492</v>
+        <v>406</v>
       </c>
       <c r="B678" s="3" t="s">
         <v>0</v>
@@ -39940,19 +39931,19 @@
         <v>3</v>
       </c>
       <c r="F678" s="4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G678" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H678" s="5">
-        <v>68462.52</v>
+        <v>0</v>
       </c>
       <c r="I678" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J678" s="5">
-        <v>0</v>
+        <v>1058092.2</v>
       </c>
       <c r="K678" s="4">
         <v>0</v>
@@ -39981,7 +39972,7 @@
     </row>
     <row r="679" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A679" s="3" t="s">
-        <v>450</v>
+        <v>490</v>
       </c>
       <c r="B679" s="3" t="s">
         <v>0</v>
@@ -39993,16 +39984,16 @@
         <v>2</v>
       </c>
       <c r="E679" s="3" t="s">
-        <v>3</v>
+        <v>453</v>
       </c>
       <c r="F679" s="4">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G679" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H679" s="5">
-        <v>0</v>
+        <v>36957.21</v>
       </c>
       <c r="I679" s="4">
         <v>0</v>
@@ -40037,7 +40028,7 @@
     </row>
     <row r="680" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A680" s="3" t="s">
-        <v>451</v>
+        <v>475</v>
       </c>
       <c r="B680" s="3" t="s">
         <v>0</v>
@@ -40052,13 +40043,13 @@
         <v>3</v>
       </c>
       <c r="F680" s="4">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G680" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H680" s="5">
-        <v>0</v>
+        <v>43365.53</v>
       </c>
       <c r="I680" s="4">
         <v>0</v>
@@ -40093,7 +40084,7 @@
     </row>
     <row r="681" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
       <c r="A681" s="3" t="s">
-        <v>406</v>
+        <v>475</v>
       </c>
       <c r="B681" s="3" t="s">
         <v>0</v>
@@ -40108,19 +40099,19 @@
         <v>3</v>
       </c>
       <c r="F681" s="4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G681" s="3" t="s">
         <v>4</v>
       </c>
       <c r="H681" s="5">
-        <v>0</v>
+        <v>52038.64</v>
       </c>
       <c r="I681" s="4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J681" s="5">
-        <v>1058092.2</v>
+        <v>0</v>
       </c>
       <c r="K681" s="4">
         <v>0</v>
@@ -40148,226 +40139,58 @@
       </c>
     </row>
     <row r="682" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A682" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="B682" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C682" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D682" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E682" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="F682" s="4">
-        <v>4</v>
-      </c>
-      <c r="G682" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H682" s="5">
-        <v>36957.21</v>
-      </c>
-      <c r="I682" s="4">
-        <v>0</v>
-      </c>
-      <c r="J682" s="5">
-        <v>0</v>
-      </c>
-      <c r="K682" s="4">
-        <v>0</v>
-      </c>
-      <c r="L682" s="5">
-        <v>0</v>
-      </c>
-      <c r="M682" s="4">
-        <v>0</v>
-      </c>
-      <c r="N682" s="5">
-        <v>0</v>
-      </c>
-      <c r="O682" s="4">
-        <v>0</v>
-      </c>
-      <c r="P682" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q682" s="4">
-        <v>0</v>
-      </c>
-      <c r="R682" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="683" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A683" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="B683" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C683" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D683" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E683" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F683" s="4">
-        <v>5</v>
-      </c>
-      <c r="G683" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H683" s="5">
-        <v>43365.53</v>
-      </c>
-      <c r="I683" s="4">
-        <v>0</v>
-      </c>
-      <c r="J683" s="5">
-        <v>0</v>
-      </c>
-      <c r="K683" s="4">
-        <v>0</v>
-      </c>
-      <c r="L683" s="5">
-        <v>0</v>
-      </c>
-      <c r="M683" s="4">
-        <v>0</v>
-      </c>
-      <c r="N683" s="5">
-        <v>0</v>
-      </c>
-      <c r="O683" s="4">
-        <v>0</v>
-      </c>
-      <c r="P683" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q683" s="4">
-        <v>0</v>
-      </c>
-      <c r="R683" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="684" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A684" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="B684" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C684" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D684" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E684" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F684" s="4">
-        <v>6</v>
-      </c>
-      <c r="G684" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H684" s="5">
-        <v>52038.64</v>
-      </c>
-      <c r="I684" s="4">
-        <v>0</v>
-      </c>
-      <c r="J684" s="5">
-        <v>0</v>
-      </c>
-      <c r="K684" s="4">
-        <v>0</v>
-      </c>
-      <c r="L684" s="5">
-        <v>0</v>
-      </c>
-      <c r="M684" s="4">
-        <v>0</v>
-      </c>
-      <c r="N684" s="5">
-        <v>0</v>
-      </c>
-      <c r="O684" s="4">
-        <v>0</v>
-      </c>
-      <c r="P684" s="5">
-        <v>0</v>
-      </c>
-      <c r="Q684" s="4">
-        <v>0</v>
-      </c>
-      <c r="R684" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="685" spans="1:18" ht="14.4" x14ac:dyDescent="0.25">
-      <c r="A685" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B685" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C685" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D685" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E685" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="F685" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="G685" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="H685" s="8">
-        <v>382779365.13999999</v>
-      </c>
-      <c r="I685" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="J685" s="8">
+      <c r="A682" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B682" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="C682" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D682" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="E682" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="F682" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="G682" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="H682" s="8">
+        <v>385531899.82999998</v>
+      </c>
+      <c r="I682" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="J682" s="8">
         <v>56071735.549999997</v>
       </c>
-      <c r="K685" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="L685" s="8">
-        <v>0</v>
-      </c>
-      <c r="M685" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="N685" s="8">
-        <v>0</v>
-      </c>
-      <c r="O685" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="P685" s="8">
-        <v>0</v>
-      </c>
-      <c r="Q685" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="R685" s="8">
+      <c r="K682" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="L682" s="8">
+        <v>0</v>
+      </c>
+      <c r="M682" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="N682" s="8">
+        <v>0</v>
+      </c>
+      <c r="O682" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="P682" s="8">
+        <v>0</v>
+      </c>
+      <c r="Q682" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="R682" s="8">
         <v>0</v>
       </c>
     </row>
